--- a/exports/motorsport_database_2026.xlsx
+++ b/exports/motorsport_database_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrea\Desktop\Sito overrevving\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9237B815-A676-4E57-BF82-5A3528EA71E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2FBFB2C-0B38-4D79-95A3-7B2104A612A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="19845" xr2:uid="{8B68D311-E33E-4B19-A776-84924D22BFC1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51600" windowHeight="19845" xr2:uid="{585B7A87-0D47-4F02-AC92-C924EEA56768}"/>
   </bookViews>
   <sheets>
     <sheet name="Calendars_2026" sheetId="4" r:id="rId1"/>
@@ -1515,7 +1515,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4C9B0E-8C47-4EE8-B71C-D2C006BE7F33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8BB0742-D075-4779-855A-66CF89C10A7D}">
   <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4253,7 +4253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613CFA2D-DB22-4CC9-8B63-265364522DB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D99BF9-5EDC-4508-928D-EBA176CC3AD1}">
   <dimension ref="A1:M1553"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -67951,7 +67951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8248567D-F1D0-46DF-971B-04CEF7B38058}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740E35D8-84AE-4C01-B0AB-485CFD4DC6C8}">
   <dimension ref="A1:H302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/exports/motorsport_database_2026.xlsx
+++ b/exports/motorsport_database_2026.xlsx
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>181.5</v>
+        <v>191.5</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -1563,20 +1563,20 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>79.5</v>
+        <v>95.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>91.5</v>
+        <v>99.5</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39">
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>93.5</v>
+        <v>100.5</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>101.5</v>
+        <v>112.5</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>133</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>112.5</v>
+        <v>132.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>117.5</v>
+        <v>125.5</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0</v>
@@ -1743,20 +1743,20 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>75.5</v>
+        <v>83</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>170</v>
+        <v>182.5</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>75.5</v>
+        <v>82.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
@@ -1803,20 +1803,20 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>72</v>
+        <v>80.5</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>173.5</v>
+        <v>185</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
@@ -1840,7 +1840,7 @@
         <v>63</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>182.5</v>
+        <v>202.5</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>60</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>185.5</v>
+        <v>205.5</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>47.5</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>44</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>201.5</v>
+        <v>221.5</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0</v>
@@ -1953,20 +1953,20 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>203.5</v>
+        <v>222.5</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51">
@@ -1983,20 +1983,20 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>208.5</v>
+        <v>223.5</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>222.5</v>
+        <v>238.5</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>224.5</v>
+        <v>241.5</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>17.5</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
         <v>17.5</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>230.5</v>
+        <v>248.5</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>232.5</v>
+        <v>251.5</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>11</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>234.5</v>
+        <v>254.5</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>241.5</v>
+        <v>261.5</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>242.5</v>
+        <v>262.5</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>0</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -2553,20 +2553,20 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71">
@@ -2583,20 +2583,20 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72">
@@ -2620,7 +2620,7 @@
         <v>146</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0</v>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
@@ -2673,20 +2673,20 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75">
@@ -2703,20 +2703,20 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
@@ -2913,20 +2913,20 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83">
@@ -2943,20 +2943,20 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84">
@@ -2973,20 +2973,20 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85">
@@ -3010,7 +3010,7 @@
         <v>61</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0</v>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
         <v>7</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>6</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>5</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>4</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>236</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
@@ -4207,14 +4207,14 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Lando Norris</t>
+          <t>Max Verstappen</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
@@ -4233,14 +4233,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Max Verstappen</t>
+          <t>Lando Norris</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
@@ -4266,7 +4266,7 @@
         <v>128</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr"/>
@@ -4292,7 +4292,7 @@
         <v>96</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr"/>
@@ -4344,7 +4344,7 @@
         <v>41</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
@@ -4370,7 +4370,7 @@
         <v>38</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
         <v>27</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
         <v>7</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
         <v>7</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
@@ -4578,7 +4578,7 @@
         <v>5</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>
@@ -35113,7 +35113,7 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G517" s="3" t="n">
@@ -35164,7 +35164,7 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G518" s="2" t="n">
@@ -35419,7 +35419,7 @@
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G523" s="3" t="n">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G525" s="3" t="n">
@@ -35776,7 +35776,7 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G530" s="2" t="n">
@@ -35827,7 +35827,7 @@
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G531" s="3" t="n">
@@ -36847,23 +36847,23 @@
       </c>
       <c r="F551" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G551" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H551" s="3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I551" s="3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J551" s="3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K551" s="3" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="L551" s="3" t="n">
         <v>0</v>
@@ -36898,23 +36898,23 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G552" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H552" s="2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K552" s="2" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L552" s="2" t="n">
         <v>0</v>
@@ -37153,23 +37153,23 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G557" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H557" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I557" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J557" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K557" s="3" t="n">
-        <v>-17</v>
+        <v>-5</v>
       </c>
       <c r="L557" s="3" t="n">
         <v>0</v>
@@ -37255,23 +37255,23 @@
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G559" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H559" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I559" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J559" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K559" s="3" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="L559" s="3" t="n">
         <v>0</v>
@@ -37510,26 +37510,26 @@
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G564" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H564" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I564" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J564" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K564" s="2" t="n">
-        <v>-21</v>
+        <v>-25</v>
       </c>
       <c r="L564" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M564" s="2" t="inlineStr">
         <is>
@@ -37561,26 +37561,26 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G565" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H565" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I565" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J565" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K565" s="3" t="n">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="L565" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -38581,26 +38581,26 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G585" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H585" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I585" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J585" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K585" s="3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L585" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -38632,26 +38632,26 @@
       </c>
       <c r="F586" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G586" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H586" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I586" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J586" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K586" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L586" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M586" s="2" t="inlineStr">
         <is>
@@ -38887,26 +38887,26 @@
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G591" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I591" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J591" s="3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K591" s="3" t="n">
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="L591" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M591" s="3" t="inlineStr">
         <is>
@@ -38989,26 +38989,26 @@
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G593" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I593" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J593" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K593" s="3" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="L593" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M593" s="3" t="inlineStr">
         <is>
@@ -39244,23 +39244,23 @@
       </c>
       <c r="F598" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G598" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H598" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K598" s="2" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="L598" s="2" t="n">
         <v>0</v>
@@ -39295,23 +39295,23 @@
       </c>
       <c r="F599" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G599" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H599" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I599" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J599" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K599" s="3" t="n">
-        <v>-26</v>
+        <v>-19</v>
       </c>
       <c r="L599" s="3" t="n">
         <v>0</v>
@@ -40315,23 +40315,23 @@
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G619" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H619" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I619" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J619" s="3" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K619" s="3" t="n">
-        <v>-13</v>
+        <v>-20</v>
       </c>
       <c r="L619" s="3" t="n">
         <v>0</v>
@@ -40366,23 +40366,23 @@
       </c>
       <c r="F620" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G620" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H620" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I620" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J620" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K620" s="2" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="L620" s="2" t="n">
         <v>0</v>
@@ -40621,23 +40621,23 @@
       </c>
       <c r="F625" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G625" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H625" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I625" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J625" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K625" s="3" t="n">
-        <v>-26</v>
+        <v>-18</v>
       </c>
       <c r="L625" s="3" t="n">
         <v>0</v>
@@ -40723,23 +40723,23 @@
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G627" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H627" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I627" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J627" s="3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K627" s="3" t="n">
-        <v>-18</v>
+        <v>-26</v>
       </c>
       <c r="L627" s="3" t="n">
         <v>0</v>
@@ -40978,7 +40978,7 @@
       </c>
       <c r="F632" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G632" s="2" t="n">
@@ -40991,10 +40991,10 @@
         <v>0</v>
       </c>
       <c r="J632" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K632" s="2" t="n">
-        <v>-42</v>
+        <v>-49</v>
       </c>
       <c r="L632" s="2" t="n">
         <v>1</v>
@@ -41029,7 +41029,7 @@
       </c>
       <c r="F633" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G633" s="3" t="n">
@@ -41042,10 +41042,10 @@
         <v>0</v>
       </c>
       <c r="J633" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K633" s="3" t="n">
-        <v>-49</v>
+        <v>-42</v>
       </c>
       <c r="L633" s="3" t="n">
         <v>1</v>
@@ -42049,26 +42049,26 @@
       </c>
       <c r="F653" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G653" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H653" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I653" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J653" s="3" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K653" s="3" t="n">
-        <v>-19</v>
+        <v>-37</v>
       </c>
       <c r="L653" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M653" s="3" t="inlineStr">
         <is>
@@ -42100,26 +42100,26 @@
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G654" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H654" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I654" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J654" s="2" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K654" s="2" t="n">
-        <v>-37</v>
+        <v>-19</v>
       </c>
       <c r="L654" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M654" s="2" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
       </c>
       <c r="F659" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G659" s="3" t="n">
@@ -42368,10 +42368,10 @@
         <v>0</v>
       </c>
       <c r="J659" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K659" s="3" t="n">
-        <v>-43</v>
+        <v>-35</v>
       </c>
       <c r="L659" s="3" t="n">
         <v>1</v>
@@ -42457,7 +42457,7 @@
       </c>
       <c r="F661" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G661" s="3" t="n">
@@ -42470,10 +42470,10 @@
         <v>0</v>
       </c>
       <c r="J661" s="3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K661" s="3" t="n">
-        <v>-35</v>
+        <v>-43</v>
       </c>
       <c r="L661" s="3" t="n">
         <v>1</v>
@@ -42712,7 +42712,7 @@
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G666" s="2" t="n">
@@ -42725,10 +42725,10 @@
         <v>0</v>
       </c>
       <c r="J666" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K666" s="2" t="n">
-        <v>-59</v>
+        <v>-66</v>
       </c>
       <c r="L666" s="2" t="n">
         <v>1</v>
@@ -42763,7 +42763,7 @@
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G667" s="3" t="n">
@@ -42776,10 +42776,10 @@
         <v>0</v>
       </c>
       <c r="J667" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K667" s="3" t="n">
-        <v>-66</v>
+        <v>-59</v>
       </c>
       <c r="L667" s="3" t="n">
         <v>1</v>
@@ -43783,23 +43783,23 @@
       </c>
       <c r="F687" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G687" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I687" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J687" s="3" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="K687" s="3" t="n">
-        <v>-34</v>
+        <v>-51</v>
       </c>
       <c r="L687" s="3" t="n">
         <v>0</v>
@@ -43834,23 +43834,23 @@
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G688" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H688" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I688" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J688" s="2" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K688" s="2" t="n">
-        <v>-51</v>
+        <v>-34</v>
       </c>
       <c r="L688" s="2" t="n">
         <v>0</v>
@@ -44089,26 +44089,26 @@
       </c>
       <c r="F693" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G693" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I693" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J693" s="3" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K693" s="3" t="n">
-        <v>-68</v>
+        <v>-55</v>
       </c>
       <c r="L693" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M693" s="3" t="inlineStr">
         <is>
@@ -44191,26 +44191,26 @@
       </c>
       <c r="F695" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G695" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I695" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J695" s="3" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K695" s="3" t="n">
-        <v>-55</v>
+        <v>-68</v>
       </c>
       <c r="L695" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -44446,26 +44446,26 @@
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G700" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H700" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I700" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J700" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K700" s="2" t="n">
-        <v>-84</v>
+        <v>-87</v>
       </c>
       <c r="L700" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M700" s="2" t="inlineStr">
         <is>
@@ -44497,26 +44497,26 @@
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G701" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H701" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I701" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J701" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K701" s="3" t="n">
-        <v>-87</v>
+        <v>-84</v>
       </c>
       <c r="L701" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
@@ -45517,26 +45517,26 @@
       </c>
       <c r="F721" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G721" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H721" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I721" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J721" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K721" s="3" t="n">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="L721" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M721" s="3" t="inlineStr">
         <is>
@@ -45568,26 +45568,26 @@
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G722" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H722" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I722" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J722" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K722" s="2" t="n">
-        <v>-60</v>
+        <v>-59</v>
       </c>
       <c r="L722" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" s="2" t="inlineStr">
         <is>
@@ -45823,26 +45823,26 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G727" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H727" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I727" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J727" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K727" s="3" t="n">
-        <v>-86</v>
+        <v>-80</v>
       </c>
       <c r="L727" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M727" s="3" t="inlineStr">
         <is>
@@ -45925,26 +45925,26 @@
       </c>
       <c r="F729" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G729" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H729" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I729" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J729" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K729" s="3" t="n">
-        <v>-80</v>
+        <v>-86</v>
       </c>
       <c r="L729" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M729" s="3" t="inlineStr">
         <is>
@@ -46180,23 +46180,23 @@
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G734" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H734" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I734" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J734" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K734" s="2" t="n">
-        <v>-105</v>
+        <v>-109</v>
       </c>
       <c r="L734" s="2" t="n">
         <v>0</v>
@@ -46231,23 +46231,23 @@
       </c>
       <c r="F735" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G735" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H735" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I735" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J735" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K735" s="3" t="n">
-        <v>-109</v>
+        <v>-105</v>
       </c>
       <c r="L735" s="3" t="n">
         <v>0</v>
@@ -47251,23 +47251,23 @@
       </c>
       <c r="F755" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G755" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I755" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J755" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K755" s="3" t="n">
-        <v>-71</v>
+        <v>-74</v>
       </c>
       <c r="L755" s="3" t="n">
         <v>0</v>
@@ -47302,23 +47302,23 @@
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G756" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H756" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I756" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J756" s="2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K756" s="2" t="n">
-        <v>-74</v>
+        <v>-71</v>
       </c>
       <c r="L756" s="2" t="n">
         <v>0</v>
@@ -47557,7 +47557,7 @@
       </c>
       <c r="F761" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G761" s="3" t="n">
@@ -47570,10 +47570,10 @@
         <v>0</v>
       </c>
       <c r="J761" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K761" s="3" t="n">
-        <v>-111</v>
+        <v>-105</v>
       </c>
       <c r="L761" s="3" t="n">
         <v>1</v>
@@ -47659,7 +47659,7 @@
       </c>
       <c r="F763" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G763" s="3" t="n">
@@ -47672,10 +47672,10 @@
         <v>0</v>
       </c>
       <c r="J763" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K763" s="3" t="n">
-        <v>-105</v>
+        <v>-111</v>
       </c>
       <c r="L763" s="3" t="n">
         <v>1</v>
@@ -47914,26 +47914,26 @@
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G768" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H768" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I768" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J768" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K768" s="2" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="L768" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M768" s="2" t="inlineStr">
         <is>
@@ -47965,26 +47965,26 @@
       </c>
       <c r="F769" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G769" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H769" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I769" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J769" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K769" s="3" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="L769" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M769" s="3" t="inlineStr">
         <is>
@@ -48985,23 +48985,23 @@
       </c>
       <c r="F789" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G789" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J789" s="3" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K789" s="3" t="n">
-        <v>-62</v>
+        <v>-76</v>
       </c>
       <c r="L789" s="3" t="n">
         <v>0</v>
@@ -49036,23 +49036,23 @@
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G790" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H790" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I790" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J790" s="2" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K790" s="2" t="n">
-        <v>-76</v>
+        <v>-62</v>
       </c>
       <c r="L790" s="2" t="n">
         <v>0</v>
@@ -49291,23 +49291,23 @@
       </c>
       <c r="F795" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G795" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I795" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J795" s="3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K795" s="3" t="n">
-        <v>-117</v>
+        <v>-112</v>
       </c>
       <c r="L795" s="3" t="n">
         <v>0</v>
@@ -49393,23 +49393,23 @@
       </c>
       <c r="F797" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G797" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I797" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J797" s="3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K797" s="3" t="n">
-        <v>-112</v>
+        <v>-117</v>
       </c>
       <c r="L797" s="3" t="n">
         <v>0</v>
@@ -49648,26 +49648,26 @@
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G802" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H802" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I802" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J802" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K802" s="2" t="n">
-        <v>-141</v>
+        <v>-134</v>
       </c>
       <c r="L802" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M802" s="2" t="inlineStr">
         <is>
@@ -49699,26 +49699,26 @@
       </c>
       <c r="F803" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G803" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H803" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I803" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J803" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K803" s="3" t="n">
-        <v>-134</v>
+        <v>-141</v>
       </c>
       <c r="L803" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M803" s="3" t="inlineStr">
         <is>
@@ -50719,23 +50719,23 @@
       </c>
       <c r="F823" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G823" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I823" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J823" s="3" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="K823" s="3" t="n">
-        <v>-57</v>
+        <v>-86</v>
       </c>
       <c r="L823" s="3" t="n">
         <v>0</v>
@@ -50770,23 +50770,23 @@
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G824" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H824" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I824" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J824" s="2" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="K824" s="2" t="n">
-        <v>-86</v>
+        <v>-57</v>
       </c>
       <c r="L824" s="2" t="n">
         <v>0</v>
@@ -51025,26 +51025,26 @@
       </c>
       <c r="F829" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G829" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I829" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J829" s="3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K829" s="3" t="n">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="L829" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M829" s="3" t="inlineStr">
         <is>
@@ -51127,26 +51127,26 @@
       </c>
       <c r="F831" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G831" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H831" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I831" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J831" s="3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K831" s="3" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="L831" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M831" s="3" t="inlineStr">
         <is>
@@ -51382,26 +51382,26 @@
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G836" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H836" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I836" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J836" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K836" s="2" t="n">
-        <v>-152</v>
+        <v>-154</v>
       </c>
       <c r="L836" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M836" s="2" t="inlineStr">
         <is>
@@ -51433,26 +51433,26 @@
       </c>
       <c r="F837" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G837" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H837" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I837" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J837" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K837" s="3" t="n">
-        <v>-154</v>
+        <v>-152</v>
       </c>
       <c r="L837" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M837" s="3" t="inlineStr">
         <is>
@@ -52453,26 +52453,26 @@
       </c>
       <c r="F857" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G857" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H857" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I857" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J857" s="3" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="K857" s="3" t="n">
-        <v>-67</v>
+        <v>-76</v>
       </c>
       <c r="L857" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M857" s="3" t="inlineStr">
         <is>
@@ -52504,26 +52504,26 @@
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G858" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H858" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I858" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J858" s="2" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K858" s="2" t="n">
-        <v>-76</v>
+        <v>-67</v>
       </c>
       <c r="L858" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M858" s="2" t="inlineStr">
         <is>
@@ -52759,26 +52759,26 @@
       </c>
       <c r="F863" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G863" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H863" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I863" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J863" s="3" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="K863" s="3" t="n">
-        <v>-133</v>
+        <v>-142</v>
       </c>
       <c r="L863" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M863" s="3" t="inlineStr">
         <is>
@@ -52861,26 +52861,26 @@
       </c>
       <c r="F865" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G865" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H865" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I865" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J865" s="3" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K865" s="3" t="n">
-        <v>-142</v>
+        <v>-133</v>
       </c>
       <c r="L865" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M865" s="3" t="inlineStr">
         <is>
@@ -53116,23 +53116,23 @@
       </c>
       <c r="F870" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G870" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H870" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I870" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J870" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K870" s="2" t="n">
-        <v>-157</v>
+        <v>-156</v>
       </c>
       <c r="L870" s="2" t="n">
         <v>0</v>
@@ -53167,23 +53167,23 @@
       </c>
       <c r="F871" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G871" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H871" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I871" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J871" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K871" s="3" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="L871" s="3" t="n">
         <v>0</v>
@@ -54187,26 +54187,26 @@
       </c>
       <c r="F891" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G891" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I891" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J891" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K891" s="3" t="n">
-        <v>-69</v>
+        <v>-65</v>
       </c>
       <c r="L891" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M891" s="3" t="inlineStr">
         <is>
@@ -54238,26 +54238,26 @@
       </c>
       <c r="F892" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G892" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H892" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I892" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J892" s="2" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K892" s="2" t="n">
-        <v>-65</v>
+        <v>-69</v>
       </c>
       <c r="L892" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M892" s="2" t="inlineStr">
         <is>
@@ -54493,17 +54493,17 @@
       </c>
       <c r="F897" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G897" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H897" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I897" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J897" s="3" t="n">
         <v>50</v>
@@ -54512,7 +54512,7 @@
         <v>-135</v>
       </c>
       <c r="L897" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M897" s="3" t="inlineStr">
         <is>
@@ -54595,17 +54595,17 @@
       </c>
       <c r="F899" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G899" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H899" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I899" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J899" s="3" t="n">
         <v>50</v>
@@ -54614,7 +54614,7 @@
         <v>-135</v>
       </c>
       <c r="L899" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M899" s="3" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
       </c>
       <c r="F904" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G904" s="2" t="n">
@@ -54863,10 +54863,10 @@
         <v>0</v>
       </c>
       <c r="J904" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K904" s="2" t="n">
-        <v>-159</v>
+        <v>-158</v>
       </c>
       <c r="L904" s="2" t="n">
         <v>1</v>
@@ -54901,7 +54901,7 @@
       </c>
       <c r="F905" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G905" s="3" t="n">
@@ -54914,10 +54914,10 @@
         <v>0</v>
       </c>
       <c r="J905" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K905" s="3" t="n">
-        <v>-158</v>
+        <v>-159</v>
       </c>
       <c r="L905" s="3" t="n">
         <v>1</v>
@@ -55921,23 +55921,23 @@
       </c>
       <c r="F925" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G925" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H925" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I925" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J925" s="3" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K925" s="3" t="n">
-        <v>-63</v>
+        <v>-66</v>
       </c>
       <c r="L925" s="3" t="n">
         <v>0</v>
@@ -55972,23 +55972,23 @@
       </c>
       <c r="F926" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G926" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H926" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I926" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J926" s="2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K926" s="2" t="n">
-        <v>-66</v>
+        <v>-63</v>
       </c>
       <c r="L926" s="2" t="n">
         <v>0</v>
@@ -56227,26 +56227,26 @@
       </c>
       <c r="F931" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G931" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I931" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J931" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K931" s="3" t="n">
-        <v>-145</v>
+        <v>-140</v>
       </c>
       <c r="L931" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M931" s="3" t="inlineStr">
         <is>
@@ -56329,26 +56329,26 @@
       </c>
       <c r="F933" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G933" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I933" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J933" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K933" s="3" t="n">
-        <v>-140</v>
+        <v>-145</v>
       </c>
       <c r="L933" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M933" s="3" t="inlineStr">
         <is>
@@ -56584,26 +56584,26 @@
       </c>
       <c r="F938" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G938" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H938" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I938" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J938" s="2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K938" s="2" t="n">
-        <v>-163</v>
+        <v>-168</v>
       </c>
       <c r="L938" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M938" s="2" t="inlineStr">
         <is>
@@ -56635,26 +56635,26 @@
       </c>
       <c r="F939" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G939" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I939" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J939" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K939" s="3" t="n">
-        <v>-168</v>
+        <v>-163</v>
       </c>
       <c r="L939" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M939" s="3" t="inlineStr">
         <is>
@@ -57655,26 +57655,26 @@
       </c>
       <c r="F959" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G959" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H959" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I959" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J959" s="3" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K959" s="3" t="n">
-        <v>-81</v>
+        <v>-91</v>
       </c>
       <c r="L959" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M959" s="3" t="inlineStr">
         <is>
@@ -57706,26 +57706,26 @@
       </c>
       <c r="F960" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G960" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H960" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I960" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J960" s="2" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K960" s="2" t="n">
-        <v>-91</v>
+        <v>-81</v>
       </c>
       <c r="L960" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M960" s="2" t="inlineStr">
         <is>
@@ -57961,23 +57961,23 @@
       </c>
       <c r="F965" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G965" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H965" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I965" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J965" s="3" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K965" s="3" t="n">
-        <v>-150</v>
+        <v>-161</v>
       </c>
       <c r="L965" s="3" t="n">
         <v>0</v>
@@ -58063,23 +58063,23 @@
       </c>
       <c r="F967" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G967" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H967" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I967" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J967" s="3" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="K967" s="3" t="n">
-        <v>-161</v>
+        <v>-150</v>
       </c>
       <c r="L967" s="3" t="n">
         <v>0</v>
@@ -58318,26 +58318,26 @@
       </c>
       <c r="F972" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G972" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H972" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I972" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J972" s="2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K972" s="2" t="n">
-        <v>-183</v>
+        <v>-193</v>
       </c>
       <c r="L972" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M972" s="2" t="inlineStr">
         <is>
@@ -58369,26 +58369,26 @@
       </c>
       <c r="F973" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G973" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H973" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I973" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J973" s="3" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K973" s="3" t="n">
-        <v>-193</v>
+        <v>-183</v>
       </c>
       <c r="L973" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M973" s="3" t="inlineStr">
         <is>
@@ -59389,23 +59389,23 @@
       </c>
       <c r="F993" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G993" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H993" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I993" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J993" s="3" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="K993" s="3" t="n">
-        <v>-78</v>
+        <v>-95</v>
       </c>
       <c r="L993" s="3" t="n">
         <v>0</v>
@@ -59440,23 +59440,23 @@
       </c>
       <c r="F994" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G994" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H994" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I994" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J994" s="2" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K994" s="2" t="n">
-        <v>-95</v>
+        <v>-78</v>
       </c>
       <c r="L994" s="2" t="n">
         <v>0</v>
@@ -59695,26 +59695,26 @@
       </c>
       <c r="F999" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G999" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H999" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I999" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J999" s="3" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K999" s="3" t="n">
-        <v>-163</v>
+        <v>-169</v>
       </c>
       <c r="L999" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M999" s="3" t="inlineStr">
         <is>
@@ -59797,26 +59797,26 @@
       </c>
       <c r="F1001" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G1001" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1001" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I1001" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1001" s="3" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K1001" s="3" t="n">
-        <v>-169</v>
+        <v>-163</v>
       </c>
       <c r="L1001" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1001" s="3" t="inlineStr">
         <is>
@@ -60052,26 +60052,26 @@
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G1006" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1006" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I1006" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1006" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K1006" s="2" t="n">
-        <v>-196</v>
+        <v>-202</v>
       </c>
       <c r="L1006" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1006" s="2" t="inlineStr">
         <is>
@@ -60103,26 +60103,26 @@
       </c>
       <c r="F1007" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G1007" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1007" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I1007" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1007" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K1007" s="3" t="n">
-        <v>-202</v>
+        <v>-196</v>
       </c>
       <c r="L1007" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1007" s="3" t="inlineStr">
         <is>
@@ -60980,10 +60980,10 @@
         <v>0</v>
       </c>
       <c r="I1024" s="2" t="n">
-        <v>12.5</v>
+        <v>32.5</v>
       </c>
       <c r="J1024" s="2" t="n">
-        <v>245.5</v>
+        <v>265.5</v>
       </c>
       <c r="K1024" s="2" t="n">
         <v>0</v>
@@ -61031,13 +61031,13 @@
         <v>25</v>
       </c>
       <c r="I1025" s="3" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J1025" s="3" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="K1025" s="3" t="n">
-        <v>-10.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L1025" s="3" t="n">
         <v>0</v>
@@ -61082,13 +61082,13 @@
         <v>13</v>
       </c>
       <c r="I1026" s="2" t="n">
-        <v>19.5</v>
+        <v>29.5</v>
       </c>
       <c r="J1026" s="2" t="n">
-        <v>181.5</v>
+        <v>191.5</v>
       </c>
       <c r="K1026" s="2" t="n">
-        <v>-64</v>
+        <v>-74</v>
       </c>
       <c r="L1026" s="2" t="n">
         <v>0</v>
@@ -61123,23 +61123,23 @@
       </c>
       <c r="F1027" s="3" t="inlineStr">
         <is>
-          <t>David Alonso</t>
+          <t>Daniel Holgado</t>
         </is>
       </c>
       <c r="G1027" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1027" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1027" s="3" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J1027" s="3" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K1027" s="3" t="n">
-        <v>-79.5</v>
+        <v>-95.5</v>
       </c>
       <c r="L1027" s="3" t="n">
         <v>0</v>
@@ -61174,23 +61174,23 @@
       </c>
       <c r="F1028" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holgado</t>
+          <t>David Alonso</t>
         </is>
       </c>
       <c r="G1028" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1028" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1028" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J1028" s="2" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="K1028" s="2" t="n">
-        <v>-91.5</v>
+        <v>-99.5</v>
       </c>
       <c r="L1028" s="2" t="n">
         <v>0</v>
@@ -61235,13 +61235,13 @@
         <v>3</v>
       </c>
       <c r="I1029" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J1029" s="3" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="K1029" s="3" t="n">
-        <v>-93.5</v>
+        <v>-100.5</v>
       </c>
       <c r="L1029" s="3" t="n">
         <v>0</v>
@@ -61286,13 +61286,13 @@
         <v>16</v>
       </c>
       <c r="I1030" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J1030" s="2" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="K1030" s="2" t="n">
-        <v>-101.5</v>
+        <v>-112.5</v>
       </c>
       <c r="L1030" s="2" t="n">
         <v>0</v>
@@ -61343,7 +61343,7 @@
         <v>133</v>
       </c>
       <c r="K1031" s="3" t="n">
-        <v>-112.5</v>
+        <v>-132.5</v>
       </c>
       <c r="L1031" s="3" t="n">
         <v>0</v>
@@ -61388,13 +61388,13 @@
         <v>7</v>
       </c>
       <c r="I1032" s="2" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="J1032" s="2" t="n">
-        <v>117.5</v>
+        <v>125.5</v>
       </c>
       <c r="K1032" s="2" t="n">
-        <v>-128</v>
+        <v>-140</v>
       </c>
       <c r="L1032" s="2" t="n">
         <v>0</v>
@@ -61429,23 +61429,23 @@
       </c>
       <c r="F1033" s="3" t="inlineStr">
         <is>
-          <t>Collin Veijer</t>
+          <t>Daniel Muñoz</t>
         </is>
       </c>
       <c r="G1033" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1033" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I1033" s="3" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="J1033" s="3" t="n">
-        <v>75.5</v>
+        <v>83</v>
       </c>
       <c r="K1033" s="3" t="n">
-        <v>-170</v>
+        <v>-182.5</v>
       </c>
       <c r="L1033" s="3" t="n">
         <v>0</v>
@@ -61490,13 +61490,13 @@
         <v>20</v>
       </c>
       <c r="I1034" s="2" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="J1034" s="2" t="n">
-        <v>75.5</v>
+        <v>82.5</v>
       </c>
       <c r="K1034" s="2" t="n">
-        <v>-170</v>
+        <v>-183</v>
       </c>
       <c r="L1034" s="2" t="n">
         <v>0</v>
@@ -61531,23 +61531,23 @@
       </c>
       <c r="F1035" s="3" t="inlineStr">
         <is>
-          <t>Daniel Muñoz</t>
+          <t>Collin Veijer</t>
         </is>
       </c>
       <c r="G1035" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1035" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I1035" s="3" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="J1035" s="3" t="n">
-        <v>72</v>
+        <v>80.5</v>
       </c>
       <c r="K1035" s="3" t="n">
-        <v>-173.5</v>
+        <v>-185</v>
       </c>
       <c r="L1035" s="3" t="n">
         <v>0</v>
@@ -61598,7 +61598,7 @@
         <v>63</v>
       </c>
       <c r="K1036" s="2" t="n">
-        <v>-182.5</v>
+        <v>-202.5</v>
       </c>
       <c r="L1036" s="2" t="n">
         <v>0</v>
@@ -61649,7 +61649,7 @@
         <v>60</v>
       </c>
       <c r="K1037" s="3" t="n">
-        <v>-185.5</v>
+        <v>-205.5</v>
       </c>
       <c r="L1037" s="3" t="n">
         <v>0</v>
@@ -61700,7 +61700,7 @@
         <v>47.5</v>
       </c>
       <c r="K1038" s="2" t="n">
-        <v>-198</v>
+        <v>-218</v>
       </c>
       <c r="L1038" s="2" t="n">
         <v>0</v>
@@ -61751,7 +61751,7 @@
         <v>44</v>
       </c>
       <c r="K1039" s="3" t="n">
-        <v>-201.5</v>
+        <v>-221.5</v>
       </c>
       <c r="L1039" s="3" t="n">
         <v>1</v>
@@ -61786,23 +61786,23 @@
       </c>
       <c r="F1040" s="2" t="inlineStr">
         <is>
-          <t>Adrian Huertas</t>
+          <t>Jose Antonio Rueda</t>
         </is>
       </c>
       <c r="G1040" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1040" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1040" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J1040" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1040" s="2" t="n">
-        <v>-203.5</v>
+        <v>-222.5</v>
       </c>
       <c r="L1040" s="2" t="n">
         <v>0</v>
@@ -61837,23 +61837,23 @@
       </c>
       <c r="F1041" s="3" t="inlineStr">
         <is>
-          <t>Jose Antonio Rueda</t>
+          <t>Adrian Huertas</t>
         </is>
       </c>
       <c r="G1041" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1041" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1041" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1041" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K1041" s="3" t="n">
-        <v>-208.5</v>
+        <v>-223.5</v>
       </c>
       <c r="L1041" s="3" t="n">
         <v>0</v>
@@ -61898,16 +61898,16 @@
         <v>0</v>
       </c>
       <c r="I1042" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1042" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K1042" s="2" t="n">
-        <v>-222.5</v>
+        <v>-238.5</v>
       </c>
       <c r="L1042" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1042" s="2" t="inlineStr">
         <is>
@@ -61949,13 +61949,13 @@
         <v>2</v>
       </c>
       <c r="I1043" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1043" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K1043" s="3" t="n">
-        <v>-224.5</v>
+        <v>-241.5</v>
       </c>
       <c r="L1043" s="3" t="n">
         <v>0</v>
@@ -62006,7 +62006,7 @@
         <v>17.5</v>
       </c>
       <c r="K1044" s="2" t="n">
-        <v>-228</v>
+        <v>-248</v>
       </c>
       <c r="L1044" s="2" t="n">
         <v>0</v>
@@ -62057,7 +62057,7 @@
         <v>17.5</v>
       </c>
       <c r="K1045" s="3" t="n">
-        <v>-228</v>
+        <v>-248</v>
       </c>
       <c r="L1045" s="3" t="n">
         <v>0</v>
@@ -62102,16 +62102,16 @@
         <v>0</v>
       </c>
       <c r="I1046" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1046" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1046" s="2" t="n">
-        <v>-230.5</v>
+        <v>-248.5</v>
       </c>
       <c r="L1046" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1046" s="2" t="inlineStr">
         <is>
@@ -62153,13 +62153,13 @@
         <v>1</v>
       </c>
       <c r="I1047" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1047" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1047" s="3" t="n">
-        <v>-232.5</v>
+        <v>-251.5</v>
       </c>
       <c r="L1047" s="3" t="n">
         <v>0</v>
@@ -62210,7 +62210,7 @@
         <v>11</v>
       </c>
       <c r="K1048" s="2" t="n">
-        <v>-234.5</v>
+        <v>-254.5</v>
       </c>
       <c r="L1048" s="2" t="n">
         <v>1</v>
@@ -62261,7 +62261,7 @@
         <v>4</v>
       </c>
       <c r="K1049" s="3" t="n">
-        <v>-241.5</v>
+        <v>-261.5</v>
       </c>
       <c r="L1049" s="3" t="n">
         <v>1</v>
@@ -62312,7 +62312,7 @@
         <v>3</v>
       </c>
       <c r="K1050" s="2" t="n">
-        <v>-242.5</v>
+        <v>-262.5</v>
       </c>
       <c r="L1050" s="2" t="n">
         <v>1</v>
@@ -62363,7 +62363,7 @@
         <v>0</v>
       </c>
       <c r="K1051" s="3" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1051" s="3" t="n">
         <v>1</v>
@@ -62414,7 +62414,7 @@
         <v>0</v>
       </c>
       <c r="K1052" s="2" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1052" s="2" t="n">
         <v>1</v>
@@ -62465,7 +62465,7 @@
         <v>0</v>
       </c>
       <c r="K1053" s="3" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1053" s="3" t="n">
         <v>1</v>
@@ -62516,7 +62516,7 @@
         <v>0</v>
       </c>
       <c r="K1054" s="2" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1054" s="2" t="n">
         <v>1</v>
@@ -62567,7 +62567,7 @@
         <v>0</v>
       </c>
       <c r="K1055" s="3" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1055" s="3" t="n">
         <v>1</v>
@@ -62618,7 +62618,7 @@
         <v>0</v>
       </c>
       <c r="K1056" s="2" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1056" s="2" t="n">
         <v>1</v>
@@ -62669,7 +62669,7 @@
         <v>0</v>
       </c>
       <c r="K1057" s="3" t="n">
-        <v>-245.5</v>
+        <v>-265.5</v>
       </c>
       <c r="L1057" s="3" t="n">
         <v>1</v>
@@ -62806,23 +62806,23 @@
       </c>
       <c r="F1060" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1060" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1060" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1060" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1060" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K1060" s="2" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="L1060" s="2" t="n">
         <v>0</v>
@@ -62857,23 +62857,23 @@
       </c>
       <c r="F1061" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1061" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1061" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1061" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1061" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K1061" s="3" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L1061" s="3" t="n">
         <v>0</v>
@@ -63010,26 +63010,26 @@
       </c>
       <c r="F1064" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1064" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1064" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I1064" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1064" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1064" s="2" t="n">
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="L1064" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1064" s="2" t="inlineStr">
         <is>
@@ -63061,26 +63061,26 @@
       </c>
       <c r="F1065" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1065" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1065" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I1065" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1065" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1065" s="3" t="n">
-        <v>-14</v>
+        <v>-25</v>
       </c>
       <c r="L1065" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1065" s="3" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
       </c>
       <c r="F1066" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1066" s="2" t="n">
@@ -63316,23 +63316,23 @@
       </c>
       <c r="F1070" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1070" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1070" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1070" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1070" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1070" s="2" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="L1070" s="2" t="n">
         <v>0</v>
@@ -63367,26 +63367,26 @@
       </c>
       <c r="F1071" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1071" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1071" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1071" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1071" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1071" s="3" t="n">
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="L1071" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1071" s="3" t="inlineStr">
         <is>
@@ -63418,23 +63418,23 @@
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1072" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1072" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I1072" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J1072" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1072" s="2" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="L1072" s="2" t="n">
         <v>0</v>
@@ -63469,23 +63469,23 @@
       </c>
       <c r="F1073" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1073" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1073" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1073" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1073" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1073" s="3" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="L1073" s="3" t="n">
         <v>0</v>
@@ -63520,26 +63520,26 @@
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1074" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1074" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1074" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1074" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1074" s="2" t="n">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="L1074" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1074" s="2" t="inlineStr">
         <is>
@@ -64438,7 +64438,7 @@
       </c>
       <c r="F1092" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1092" s="2" t="n">
@@ -64451,10 +64451,10 @@
         <v>0</v>
       </c>
       <c r="J1092" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K1092" s="2" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="L1092" s="2" t="n">
         <v>1</v>
@@ -64489,7 +64489,7 @@
       </c>
       <c r="F1093" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1093" s="3" t="n">
@@ -64502,10 +64502,10 @@
         <v>0</v>
       </c>
       <c r="J1093" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K1093" s="3" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L1093" s="3" t="n">
         <v>1</v>
@@ -64642,7 +64642,7 @@
       </c>
       <c r="F1096" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1096" s="2" t="n">
@@ -64655,10 +64655,10 @@
         <v>0</v>
       </c>
       <c r="J1096" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1096" s="2" t="n">
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="L1096" s="2" t="n">
         <v>1</v>
@@ -64693,7 +64693,7 @@
       </c>
       <c r="F1097" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1097" s="3" t="n">
@@ -64706,10 +64706,10 @@
         <v>0</v>
       </c>
       <c r="J1097" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1097" s="3" t="n">
-        <v>-14</v>
+        <v>-25</v>
       </c>
       <c r="L1097" s="3" t="n">
         <v>1</v>
@@ -64744,7 +64744,7 @@
       </c>
       <c r="F1098" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1098" s="2" t="n">
@@ -64948,7 +64948,7 @@
       </c>
       <c r="F1102" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1102" s="2" t="n">
@@ -64961,10 +64961,10 @@
         <v>0</v>
       </c>
       <c r="J1102" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1102" s="2" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="L1102" s="2" t="n">
         <v>1</v>
@@ -64999,7 +64999,7 @@
       </c>
       <c r="F1103" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1103" s="3" t="n">
@@ -65012,10 +65012,10 @@
         <v>0</v>
       </c>
       <c r="J1103" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1103" s="3" t="n">
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="L1103" s="3" t="n">
         <v>1</v>
@@ -65050,7 +65050,7 @@
       </c>
       <c r="F1104" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1104" s="2" t="n">
@@ -65063,10 +65063,10 @@
         <v>0</v>
       </c>
       <c r="J1104" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1104" s="2" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="L1104" s="2" t="n">
         <v>1</v>
@@ -65101,7 +65101,7 @@
       </c>
       <c r="F1105" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1105" s="3" t="n">
@@ -65114,10 +65114,10 @@
         <v>0</v>
       </c>
       <c r="J1105" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1105" s="3" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="L1105" s="3" t="n">
         <v>1</v>
@@ -65152,7 +65152,7 @@
       </c>
       <c r="F1106" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1106" s="2" t="n">
@@ -65165,10 +65165,10 @@
         <v>0</v>
       </c>
       <c r="J1106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1106" s="2" t="n">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="L1106" s="2" t="n">
         <v>1</v>
@@ -66070,23 +66070,23 @@
       </c>
       <c r="F1124" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1124" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I1124" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J1124" s="2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K1124" s="2" t="n">
-        <v>-11</v>
+        <v>-20</v>
       </c>
       <c r="L1124" s="2" t="n">
         <v>0</v>
@@ -66121,23 +66121,23 @@
       </c>
       <c r="F1125" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1125" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I1125" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J1125" s="3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K1125" s="3" t="n">
-        <v>-20</v>
+        <v>-11</v>
       </c>
       <c r="L1125" s="3" t="n">
         <v>0</v>
@@ -66274,26 +66274,26 @@
       </c>
       <c r="F1128" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1128" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I1128" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1128" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K1128" s="2" t="n">
-        <v>-36</v>
+        <v>-29</v>
       </c>
       <c r="L1128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1128" s="2" t="inlineStr">
         <is>
@@ -66325,26 +66325,26 @@
       </c>
       <c r="F1129" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1129" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I1129" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1129" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K1129" s="3" t="n">
-        <v>-29</v>
+        <v>-32</v>
       </c>
       <c r="L1129" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1129" s="3" t="inlineStr">
         <is>
@@ -66376,23 +66376,23 @@
       </c>
       <c r="F1130" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1130" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I1130" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J1130" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K1130" s="2" t="n">
-        <v>-32</v>
+        <v>-36</v>
       </c>
       <c r="L1130" s="2" t="n">
         <v>0</v>
@@ -66580,7 +66580,7 @@
       </c>
       <c r="F1134" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1134" s="2" t="n">
@@ -66593,10 +66593,10 @@
         <v>0</v>
       </c>
       <c r="J1134" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1134" s="2" t="n">
-        <v>-34</v>
+        <v>-32</v>
       </c>
       <c r="L1134" s="2" t="n">
         <v>1</v>
@@ -66631,7 +66631,7 @@
       </c>
       <c r="F1135" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1135" s="3" t="n">
@@ -66644,10 +66644,10 @@
         <v>0</v>
       </c>
       <c r="J1135" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1135" s="3" t="n">
-        <v>-37</v>
+        <v>-40</v>
       </c>
       <c r="L1135" s="3" t="n">
         <v>1</v>
@@ -66682,7 +66682,7 @@
       </c>
       <c r="F1136" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1136" s="2" t="n">
@@ -66695,10 +66695,10 @@
         <v>0</v>
       </c>
       <c r="J1136" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1136" s="2" t="n">
-        <v>-32</v>
+        <v>-34</v>
       </c>
       <c r="L1136" s="2" t="n">
         <v>1</v>
@@ -66733,26 +66733,26 @@
       </c>
       <c r="F1137" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1137" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1137" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I1137" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1137" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K1137" s="3" t="n">
-        <v>-32</v>
+        <v>-37</v>
       </c>
       <c r="L1137" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1137" s="3" t="inlineStr">
         <is>
@@ -66784,26 +66784,26 @@
       </c>
       <c r="F1138" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1138" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I1138" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1138" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1138" s="2" t="n">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="L1138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1138" s="2" t="inlineStr">
         <is>
@@ -67702,23 +67702,23 @@
       </c>
       <c r="F1156" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1156" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I1156" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J1156" s="2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K1156" s="2" t="n">
-        <v>-23</v>
+        <v>-39</v>
       </c>
       <c r="L1156" s="2" t="n">
         <v>0</v>
@@ -67753,23 +67753,23 @@
       </c>
       <c r="F1157" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1157" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1157" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I1157" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J1157" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K1157" s="3" t="n">
-        <v>-39</v>
+        <v>-23</v>
       </c>
       <c r="L1157" s="3" t="n">
         <v>0</v>
@@ -67906,23 +67906,23 @@
       </c>
       <c r="F1160" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1160" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I1160" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1160" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K1160" s="2" t="n">
-        <v>-57</v>
+        <v>-43</v>
       </c>
       <c r="L1160" s="2" t="n">
         <v>0</v>
@@ -67957,26 +67957,26 @@
       </c>
       <c r="F1161" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1161" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I1161" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1161" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K1161" s="3" t="n">
-        <v>-43</v>
+        <v>-57</v>
       </c>
       <c r="L1161" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1161" s="3" t="inlineStr">
         <is>
@@ -68008,17 +68008,17 @@
       </c>
       <c r="F1162" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1162" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I1162" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1162" s="2" t="n">
         <v>8</v>
@@ -68027,7 +68027,7 @@
         <v>-57</v>
       </c>
       <c r="L1162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1162" s="2" t="inlineStr">
         <is>
@@ -68212,23 +68212,23 @@
       </c>
       <c r="F1166" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1166" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1166" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1166" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K1166" s="2" t="n">
-        <v>-54</v>
+        <v>-50</v>
       </c>
       <c r="L1166" s="2" t="n">
         <v>0</v>
@@ -68263,26 +68263,26 @@
       </c>
       <c r="F1167" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1167" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1167" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1167" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1167" s="3" t="n">
-        <v>-59</v>
+        <v>-65</v>
       </c>
       <c r="L1167" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1167" s="3" t="inlineStr">
         <is>
@@ -68314,23 +68314,23 @@
       </c>
       <c r="F1168" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1168" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I1168" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J1168" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K1168" s="2" t="n">
-        <v>-50</v>
+        <v>-54</v>
       </c>
       <c r="L1168" s="2" t="n">
         <v>0</v>
@@ -68365,26 +68365,26 @@
       </c>
       <c r="F1169" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1169" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1169" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1169" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1169" s="3" t="n">
-        <v>-57</v>
+        <v>-59</v>
       </c>
       <c r="L1169" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1169" s="3" t="inlineStr">
         <is>
@@ -68416,7 +68416,7 @@
       </c>
       <c r="F1170" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1170" s="2" t="n">
@@ -68429,10 +68429,10 @@
         <v>0</v>
       </c>
       <c r="J1170" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1170" s="2" t="n">
-        <v>-65</v>
+        <v>-57</v>
       </c>
       <c r="L1170" s="2" t="n">
         <v>1</v>
@@ -69334,26 +69334,26 @@
       </c>
       <c r="F1188" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1188" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1188" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1188" s="2" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K1188" s="2" t="n">
-        <v>-48</v>
+        <v>-62</v>
       </c>
       <c r="L1188" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1188" s="2" t="inlineStr">
         <is>
@@ -69385,26 +69385,26 @@
       </c>
       <c r="F1189" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1189" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1189" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I1189" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1189" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K1189" s="3" t="n">
-        <v>-62</v>
+        <v>-48</v>
       </c>
       <c r="L1189" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1189" s="3" t="inlineStr">
         <is>
@@ -69538,23 +69538,23 @@
       </c>
       <c r="F1192" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1192" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I1192" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J1192" s="2" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="K1192" s="2" t="n">
-        <v>-75</v>
+        <v>-52</v>
       </c>
       <c r="L1192" s="2" t="n">
         <v>0</v>
@@ -69589,23 +69589,23 @@
       </c>
       <c r="F1193" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1193" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I1193" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J1193" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K1193" s="3" t="n">
-        <v>-52</v>
+        <v>-62</v>
       </c>
       <c r="L1193" s="3" t="n">
         <v>0</v>
@@ -69640,23 +69640,23 @@
       </c>
       <c r="F1194" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1194" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1194" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I1194" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J1194" s="2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K1194" s="2" t="n">
-        <v>-62</v>
+        <v>-75</v>
       </c>
       <c r="L1194" s="2" t="n">
         <v>0</v>
@@ -69844,26 +69844,26 @@
       </c>
       <c r="F1198" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1198" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I1198" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1198" s="2" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K1198" s="2" t="n">
-        <v>-79</v>
+        <v>-62</v>
       </c>
       <c r="L1198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1198" s="2" t="inlineStr">
         <is>
@@ -69895,7 +69895,7 @@
       </c>
       <c r="F1199" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1199" s="3" t="n">
@@ -69908,10 +69908,10 @@
         <v>0</v>
       </c>
       <c r="J1199" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1199" s="3" t="n">
-        <v>-84</v>
+        <v>-90</v>
       </c>
       <c r="L1199" s="3" t="n">
         <v>1</v>
@@ -69946,26 +69946,26 @@
       </c>
       <c r="F1200" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1200" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I1200" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J1200" s="2" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K1200" s="2" t="n">
-        <v>-62</v>
+        <v>-79</v>
       </c>
       <c r="L1200" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1200" s="2" t="inlineStr">
         <is>
@@ -69997,26 +69997,26 @@
       </c>
       <c r="F1201" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1201" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1201" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I1201" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1201" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K1201" s="3" t="n">
-        <v>-74</v>
+        <v>-84</v>
       </c>
       <c r="L1201" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1201" s="3" t="inlineStr">
         <is>
@@ -70048,26 +70048,26 @@
       </c>
       <c r="F1202" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1202" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1202" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I1202" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1202" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K1202" s="2" t="n">
-        <v>-90</v>
+        <v>-74</v>
       </c>
       <c r="L1202" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1202" s="2" t="inlineStr">
         <is>
@@ -70966,26 +70966,26 @@
       </c>
       <c r="F1220" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1220" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I1220" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J1220" s="2" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="K1220" s="2" t="n">
-        <v>-53</v>
+        <v>-87</v>
       </c>
       <c r="L1220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1220" s="2" t="inlineStr">
         <is>
@@ -71017,26 +71017,26 @@
       </c>
       <c r="F1221" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1221" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1221" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I1221" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1221" s="3" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="K1221" s="3" t="n">
-        <v>-87</v>
+        <v>-53</v>
       </c>
       <c r="L1221" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1221" s="3" t="inlineStr">
         <is>
@@ -71170,23 +71170,23 @@
       </c>
       <c r="F1224" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1224" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1224" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1224" s="2" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K1224" s="2" t="n">
-        <v>-90</v>
+        <v>-68</v>
       </c>
       <c r="L1224" s="2" t="n">
         <v>0</v>
@@ -71221,23 +71221,23 @@
       </c>
       <c r="F1225" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1225" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1225" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I1225" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J1225" s="3" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K1225" s="3" t="n">
-        <v>-68</v>
+        <v>-83</v>
       </c>
       <c r="L1225" s="3" t="n">
         <v>0</v>
@@ -71272,23 +71272,23 @@
       </c>
       <c r="F1226" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1226" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I1226" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1226" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K1226" s="2" t="n">
-        <v>-83</v>
+        <v>-90</v>
       </c>
       <c r="L1226" s="2" t="n">
         <v>0</v>
@@ -71476,23 +71476,23 @@
       </c>
       <c r="F1230" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1230" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I1230" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J1230" s="2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K1230" s="2" t="n">
-        <v>-96</v>
+        <v>-85</v>
       </c>
       <c r="L1230" s="2" t="n">
         <v>0</v>
@@ -71527,7 +71527,7 @@
       </c>
       <c r="F1231" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1231" s="3" t="n">
@@ -71540,10 +71540,10 @@
         <v>0</v>
       </c>
       <c r="J1231" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1231" s="3" t="n">
-        <v>-109</v>
+        <v>-115</v>
       </c>
       <c r="L1231" s="3" t="n">
         <v>1</v>
@@ -71578,23 +71578,23 @@
       </c>
       <c r="F1232" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1232" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1232" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I1232" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1232" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K1232" s="2" t="n">
-        <v>-85</v>
+        <v>-96</v>
       </c>
       <c r="L1232" s="2" t="n">
         <v>0</v>
@@ -71629,26 +71629,26 @@
       </c>
       <c r="F1233" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1233" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1233" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I1233" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1233" s="3" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K1233" s="3" t="n">
-        <v>-92</v>
+        <v>-109</v>
       </c>
       <c r="L1233" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1233" s="3" t="inlineStr">
         <is>
@@ -71680,26 +71680,26 @@
       </c>
       <c r="F1234" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1234" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1234" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I1234" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1234" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K1234" s="2" t="n">
-        <v>-115</v>
+        <v>-92</v>
       </c>
       <c r="L1234" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1234" s="2" t="inlineStr">
         <is>
@@ -72598,23 +72598,23 @@
       </c>
       <c r="F1252" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1252" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I1252" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1252" s="2" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="K1252" s="2" t="n">
-        <v>-38</v>
+        <v>-67</v>
       </c>
       <c r="L1252" s="2" t="n">
         <v>0</v>
@@ -72649,23 +72649,23 @@
       </c>
       <c r="F1253" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1253" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1253" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I1253" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1253" s="3" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="K1253" s="3" t="n">
-        <v>-67</v>
+        <v>-38</v>
       </c>
       <c r="L1253" s="3" t="n">
         <v>0</v>
@@ -72802,23 +72802,23 @@
       </c>
       <c r="F1256" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1256" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I1256" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J1256" s="2" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K1256" s="2" t="n">
-        <v>-79</v>
+        <v>-65</v>
       </c>
       <c r="L1256" s="2" t="n">
         <v>0</v>
@@ -72853,23 +72853,23 @@
       </c>
       <c r="F1257" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1257" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1257" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I1257" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J1257" s="3" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="K1257" s="3" t="n">
-        <v>-65</v>
+        <v>-84</v>
       </c>
       <c r="L1257" s="3" t="n">
         <v>0</v>
@@ -72904,23 +72904,23 @@
       </c>
       <c r="F1258" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1258" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I1258" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J1258" s="2" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K1258" s="2" t="n">
-        <v>-84</v>
+        <v>-79</v>
       </c>
       <c r="L1258" s="2" t="n">
         <v>0</v>
@@ -73108,26 +73108,26 @@
       </c>
       <c r="F1262" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1262" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1262" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I1262" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1262" s="2" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K1262" s="2" t="n">
-        <v>-101</v>
+        <v>-79</v>
       </c>
       <c r="L1262" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1262" s="2" t="inlineStr">
         <is>
@@ -73159,17 +73159,17 @@
       </c>
       <c r="F1263" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1263" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1263" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I1263" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J1263" s="3" t="n">
         <v>13</v>
@@ -73210,26 +73210,26 @@
       </c>
       <c r="F1264" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1264" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I1264" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1264" s="2" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K1264" s="2" t="n">
-        <v>-79</v>
+        <v>-101</v>
       </c>
       <c r="L1264" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1264" s="2" t="inlineStr">
         <is>
@@ -73261,23 +73261,23 @@
       </c>
       <c r="F1265" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1265" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1265" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1265" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1265" s="3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K1265" s="3" t="n">
-        <v>-87</v>
+        <v>-107</v>
       </c>
       <c r="L1265" s="3" t="n">
         <v>0</v>
@@ -73312,23 +73312,23 @@
       </c>
       <c r="F1266" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1266" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I1266" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1266" s="2" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K1266" s="2" t="n">
-        <v>-107</v>
+        <v>-87</v>
       </c>
       <c r="L1266" s="2" t="n">
         <v>0</v>
@@ -74230,23 +74230,23 @@
       </c>
       <c r="F1284" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1284" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1284" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I1284" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1284" s="2" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="K1284" s="2" t="n">
-        <v>-47</v>
+        <v>-79</v>
       </c>
       <c r="L1284" s="2" t="n">
         <v>0</v>
@@ -74281,23 +74281,23 @@
       </c>
       <c r="F1285" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1285" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1285" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1285" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J1285" s="3" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="K1285" s="3" t="n">
-        <v>-79</v>
+        <v>-47</v>
       </c>
       <c r="L1285" s="3" t="n">
         <v>0</v>
@@ -74434,7 +74434,7 @@
       </c>
       <c r="F1288" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1288" s="2" t="n">
@@ -74447,10 +74447,10 @@
         <v>0</v>
       </c>
       <c r="J1288" s="2" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K1288" s="2" t="n">
-        <v>-104</v>
+        <v>-90</v>
       </c>
       <c r="L1288" s="2" t="n">
         <v>1</v>
@@ -74485,26 +74485,26 @@
       </c>
       <c r="F1289" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1289" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1289" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1289" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1289" s="3" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K1289" s="3" t="n">
-        <v>-90</v>
+        <v>-108</v>
       </c>
       <c r="L1289" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1289" s="3" t="inlineStr">
         <is>
@@ -74536,26 +74536,26 @@
       </c>
       <c r="F1290" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1290" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1290" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1290" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1290" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K1290" s="2" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="L1290" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1290" s="2" t="inlineStr">
         <is>
@@ -74740,23 +74740,23 @@
       </c>
       <c r="F1294" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1294" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1294" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I1294" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1294" s="2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K1294" s="2" t="n">
-        <v>-119</v>
+        <v>-101</v>
       </c>
       <c r="L1294" s="2" t="n">
         <v>0</v>
@@ -74791,23 +74791,23 @@
       </c>
       <c r="F1295" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1295" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1295" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1295" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1295" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K1295" s="3" t="n">
-        <v>-128</v>
+        <v>-126</v>
       </c>
       <c r="L1295" s="3" t="n">
         <v>0</v>
@@ -74842,23 +74842,23 @@
       </c>
       <c r="F1296" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1296" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1296" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I1296" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J1296" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K1296" s="2" t="n">
-        <v>-101</v>
+        <v>-119</v>
       </c>
       <c r="L1296" s="2" t="n">
         <v>0</v>
@@ -74893,26 +74893,26 @@
       </c>
       <c r="F1297" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1297" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1297" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I1297" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1297" s="3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K1297" s="3" t="n">
-        <v>-112</v>
+        <v>-128</v>
       </c>
       <c r="L1297" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1297" s="3" t="inlineStr">
         <is>
@@ -74944,26 +74944,26 @@
       </c>
       <c r="F1298" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1298" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1298" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I1298" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1298" s="2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K1298" s="2" t="n">
-        <v>-126</v>
+        <v>-112</v>
       </c>
       <c r="L1298" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1298" s="2" t="inlineStr">
         <is>
@@ -75862,23 +75862,23 @@
       </c>
       <c r="F1316" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1316" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1316" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I1316" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1316" s="2" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="K1316" s="2" t="n">
-        <v>-53</v>
+        <v>-75</v>
       </c>
       <c r="L1316" s="2" t="n">
         <v>0</v>
@@ -75913,23 +75913,23 @@
       </c>
       <c r="F1317" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1317" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1317" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I1317" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1317" s="3" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="K1317" s="3" t="n">
-        <v>-75</v>
+        <v>-53</v>
       </c>
       <c r="L1317" s="3" t="n">
         <v>0</v>
@@ -76066,17 +76066,17 @@
       </c>
       <c r="F1320" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1320" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1320" s="2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I1320" s="2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J1320" s="2" t="n">
         <v>66</v>
@@ -76117,23 +76117,23 @@
       </c>
       <c r="F1321" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1321" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1321" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I1321" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J1321" s="3" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="K1321" s="3" t="n">
-        <v>-95</v>
+        <v>-119</v>
       </c>
       <c r="L1321" s="3" t="n">
         <v>0</v>
@@ -76168,23 +76168,23 @@
       </c>
       <c r="F1322" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1322" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1322" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I1322" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J1322" s="2" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K1322" s="2" t="n">
-        <v>-119</v>
+        <v>-95</v>
       </c>
       <c r="L1322" s="2" t="n">
         <v>0</v>
@@ -76372,7 +76372,7 @@
       </c>
       <c r="F1326" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1326" s="2" t="n">
@@ -76385,10 +76385,10 @@
         <v>0</v>
       </c>
       <c r="J1326" s="2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K1326" s="2" t="n">
-        <v>-135</v>
+        <v>-117</v>
       </c>
       <c r="L1326" s="2" t="n">
         <v>1</v>
@@ -76423,23 +76423,23 @@
       </c>
       <c r="F1327" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1327" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1327" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I1327" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J1327" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K1327" s="3" t="n">
-        <v>-136</v>
+        <v>-140</v>
       </c>
       <c r="L1327" s="3" t="n">
         <v>0</v>
@@ -76474,7 +76474,7 @@
       </c>
       <c r="F1328" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1328" s="2" t="n">
@@ -76487,10 +76487,10 @@
         <v>0</v>
       </c>
       <c r="J1328" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K1328" s="2" t="n">
-        <v>-117</v>
+        <v>-135</v>
       </c>
       <c r="L1328" s="2" t="n">
         <v>1</v>
@@ -76525,26 +76525,26 @@
       </c>
       <c r="F1329" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1329" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1329" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I1329" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1329" s="3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K1329" s="3" t="n">
-        <v>-128</v>
+        <v>-136</v>
       </c>
       <c r="L1329" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1329" s="3" t="inlineStr">
         <is>
@@ -76576,26 +76576,26 @@
       </c>
       <c r="F1330" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1330" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1330" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I1330" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1330" s="2" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K1330" s="2" t="n">
-        <v>-140</v>
+        <v>-128</v>
       </c>
       <c r="L1330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1330" s="2" t="inlineStr">
         <is>
@@ -77494,26 +77494,26 @@
       </c>
       <c r="F1348" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1348" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1348" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I1348" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1348" s="2" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K1348" s="2" t="n">
-        <v>-78</v>
+        <v>-90</v>
       </c>
       <c r="L1348" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1348" s="2" t="inlineStr">
         <is>
@@ -77545,26 +77545,26 @@
       </c>
       <c r="F1349" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1349" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1349" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I1349" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1349" s="3" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K1349" s="3" t="n">
-        <v>-90</v>
+        <v>-78</v>
       </c>
       <c r="L1349" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1349" s="3" t="inlineStr">
         <is>
@@ -77698,26 +77698,26 @@
       </c>
       <c r="F1352" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1352" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1352" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I1352" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1352" s="2" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K1352" s="2" t="n">
-        <v>-111</v>
+        <v>-120</v>
       </c>
       <c r="L1352" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1352" s="2" t="inlineStr">
         <is>
@@ -77749,26 +77749,26 @@
       </c>
       <c r="F1353" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1353" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1353" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1353" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1353" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="K1353" s="3" t="n">
-        <v>-120</v>
+        <v>-142</v>
       </c>
       <c r="L1353" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1353" s="3" t="inlineStr">
         <is>
@@ -77800,23 +77800,23 @@
       </c>
       <c r="F1354" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1354" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1354" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I1354" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1354" s="2" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="K1354" s="2" t="n">
-        <v>-142</v>
+        <v>-111</v>
       </c>
       <c r="L1354" s="2" t="n">
         <v>0</v>
@@ -78004,23 +78004,23 @@
       </c>
       <c r="F1358" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1358" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1358" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1358" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J1358" s="2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K1358" s="2" t="n">
-        <v>-154</v>
+        <v>-138</v>
       </c>
       <c r="L1358" s="2" t="n">
         <v>0</v>
@@ -78055,23 +78055,23 @@
       </c>
       <c r="F1359" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1359" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1359" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1359" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1359" s="3" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K1359" s="3" t="n">
-        <v>-153</v>
+        <v>-158</v>
       </c>
       <c r="L1359" s="3" t="n">
         <v>0</v>
@@ -78106,23 +78106,23 @@
       </c>
       <c r="F1360" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1360" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1360" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1360" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1360" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K1360" s="2" t="n">
-        <v>-138</v>
+        <v>-154</v>
       </c>
       <c r="L1360" s="2" t="n">
         <v>0</v>
@@ -78157,23 +78157,23 @@
       </c>
       <c r="F1361" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1361" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1361" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I1361" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1361" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K1361" s="3" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="L1361" s="3" t="n">
         <v>0</v>
@@ -78208,23 +78208,23 @@
       </c>
       <c r="F1362" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1362" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1362" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I1362" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J1362" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K1362" s="2" t="n">
-        <v>-158</v>
+        <v>-152</v>
       </c>
       <c r="L1362" s="2" t="n">
         <v>0</v>
@@ -79126,23 +79126,23 @@
       </c>
       <c r="F1380" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1380" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1380" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I1380" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J1380" s="2" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K1380" s="2" t="n">
-        <v>-93</v>
+        <v>-85</v>
       </c>
       <c r="L1380" s="2" t="n">
         <v>0</v>
@@ -79177,23 +79177,23 @@
       </c>
       <c r="F1381" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1381" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1381" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I1381" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J1381" s="3" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K1381" s="3" t="n">
-        <v>-85</v>
+        <v>-93</v>
       </c>
       <c r="L1381" s="3" t="n">
         <v>0</v>
@@ -79330,23 +79330,23 @@
       </c>
       <c r="F1384" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1384" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1384" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I1384" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J1384" s="2" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K1384" s="2" t="n">
-        <v>-127</v>
+        <v>-132</v>
       </c>
       <c r="L1384" s="2" t="n">
         <v>0</v>
@@ -79381,23 +79381,23 @@
       </c>
       <c r="F1385" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1385" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1385" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I1385" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J1385" s="3" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="K1385" s="3" t="n">
-        <v>-132</v>
+        <v>-146</v>
       </c>
       <c r="L1385" s="3" t="n">
         <v>0</v>
@@ -79432,23 +79432,23 @@
       </c>
       <c r="F1386" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1386" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1386" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I1386" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J1386" s="2" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="K1386" s="2" t="n">
-        <v>-146</v>
+        <v>-127</v>
       </c>
       <c r="L1386" s="2" t="n">
         <v>0</v>
@@ -79636,7 +79636,7 @@
       </c>
       <c r="F1390" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1390" s="2" t="n">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="J1390" s="2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K1390" s="2" t="n">
-        <v>-174</v>
+        <v>-158</v>
       </c>
       <c r="L1390" s="2" t="n">
         <v>1</v>
@@ -79687,23 +79687,23 @@
       </c>
       <c r="F1391" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1391" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1391" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I1391" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1391" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K1391" s="3" t="n">
-        <v>-171</v>
+        <v>-168</v>
       </c>
       <c r="L1391" s="3" t="n">
         <v>0</v>
@@ -79738,7 +79738,7 @@
       </c>
       <c r="F1392" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1392" s="2" t="n">
@@ -79751,10 +79751,10 @@
         <v>0</v>
       </c>
       <c r="J1392" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K1392" s="2" t="n">
-        <v>-158</v>
+        <v>-174</v>
       </c>
       <c r="L1392" s="2" t="n">
         <v>1</v>
@@ -79789,23 +79789,23 @@
       </c>
       <c r="F1393" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1393" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1393" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I1393" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1393" s="3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K1393" s="3" t="n">
-        <v>-166</v>
+        <v>-171</v>
       </c>
       <c r="L1393" s="3" t="n">
         <v>0</v>
@@ -79840,23 +79840,23 @@
       </c>
       <c r="F1394" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1394" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1394" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I1394" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1394" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K1394" s="2" t="n">
-        <v>-168</v>
+        <v>-166</v>
       </c>
       <c r="L1394" s="2" t="n">
         <v>0</v>
@@ -80758,26 +80758,26 @@
       </c>
       <c r="F1412" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1412" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1412" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I1412" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J1412" s="2" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K1412" s="2" t="n">
-        <v>-73</v>
+        <v>-85</v>
       </c>
       <c r="L1412" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1412" s="2" t="inlineStr">
         <is>
@@ -80809,26 +80809,26 @@
       </c>
       <c r="F1413" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1413" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1413" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I1413" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1413" s="3" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K1413" s="3" t="n">
-        <v>-85</v>
+        <v>-73</v>
       </c>
       <c r="L1413" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1413" s="3" t="inlineStr">
         <is>
@@ -80962,26 +80962,26 @@
       </c>
       <c r="F1416" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1416" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1416" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I1416" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1416" s="2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K1416" s="2" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="L1416" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1416" s="2" t="inlineStr">
         <is>
@@ -81013,23 +81013,23 @@
       </c>
       <c r="F1417" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1417" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1417" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1417" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1417" s="3" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="K1417" s="3" t="n">
-        <v>-125</v>
+        <v>-140</v>
       </c>
       <c r="L1417" s="3" t="n">
         <v>0</v>
@@ -81064,26 +81064,26 @@
       </c>
       <c r="F1418" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1418" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1418" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I1418" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1418" s="2" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K1418" s="2" t="n">
-        <v>-140</v>
+        <v>-127</v>
       </c>
       <c r="L1418" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1418" s="2" t="inlineStr">
         <is>
@@ -81268,23 +81268,23 @@
       </c>
       <c r="F1422" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1422" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1422" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I1422" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1422" s="2" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="K1422" s="2" t="n">
-        <v>-170</v>
+        <v>-147</v>
       </c>
       <c r="L1422" s="2" t="n">
         <v>0</v>
@@ -81319,23 +81319,23 @@
       </c>
       <c r="F1423" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1423" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1423" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I1423" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1423" s="3" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K1423" s="3" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="L1423" s="3" t="n">
         <v>0</v>
@@ -81370,23 +81370,23 @@
       </c>
       <c r="F1424" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1424" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1424" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I1424" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J1424" s="2" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="K1424" s="2" t="n">
-        <v>-147</v>
+        <v>-170</v>
       </c>
       <c r="L1424" s="2" t="n">
         <v>0</v>
@@ -81421,23 +81421,23 @@
       </c>
       <c r="F1425" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1425" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1425" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1425" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J1425" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K1425" s="3" t="n">
-        <v>-158</v>
+        <v>-161</v>
       </c>
       <c r="L1425" s="3" t="n">
         <v>0</v>
@@ -81472,23 +81472,23 @@
       </c>
       <c r="F1426" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1426" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1426" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I1426" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J1426" s="2" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K1426" s="2" t="n">
-        <v>-155</v>
+        <v>-158</v>
       </c>
       <c r="L1426" s="2" t="n">
         <v>0</v>
@@ -82390,23 +82390,23 @@
       </c>
       <c r="F1444" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1444" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1444" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I1444" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J1444" s="2" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="K1444" s="2" t="n">
-        <v>-85</v>
+        <v>-99</v>
       </c>
       <c r="L1444" s="2" t="n">
         <v>0</v>
@@ -82441,23 +82441,23 @@
       </c>
       <c r="F1445" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1445" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1445" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1445" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J1445" s="3" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="K1445" s="3" t="n">
-        <v>-99</v>
+        <v>-85</v>
       </c>
       <c r="L1445" s="3" t="n">
         <v>0</v>
@@ -82594,26 +82594,26 @@
       </c>
       <c r="F1448" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1448" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1448" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I1448" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1448" s="2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K1448" s="2" t="n">
-        <v>-148</v>
+        <v>-150</v>
       </c>
       <c r="L1448" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1448" s="2" t="inlineStr">
         <is>
@@ -82645,26 +82645,26 @@
       </c>
       <c r="F1449" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1449" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1449" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I1449" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1449" s="3" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="K1449" s="3" t="n">
-        <v>-150</v>
+        <v>-160</v>
       </c>
       <c r="L1449" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1449" s="3" t="inlineStr">
         <is>
@@ -82696,23 +82696,23 @@
       </c>
       <c r="F1450" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1450" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1450" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1450" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1450" s="2" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K1450" s="2" t="n">
-        <v>-160</v>
+        <v>-148</v>
       </c>
       <c r="L1450" s="2" t="n">
         <v>0</v>
@@ -82900,26 +82900,26 @@
       </c>
       <c r="F1454" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1454" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1454" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I1454" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1454" s="2" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K1454" s="2" t="n">
-        <v>-186</v>
+        <v>-172</v>
       </c>
       <c r="L1454" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1454" s="2" t="inlineStr">
         <is>
@@ -82951,23 +82951,23 @@
       </c>
       <c r="F1455" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1455" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1455" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I1455" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J1455" s="3" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="K1455" s="3" t="n">
-        <v>-183</v>
+        <v>-174</v>
       </c>
       <c r="L1455" s="3" t="n">
         <v>0</v>
@@ -83002,26 +83002,26 @@
       </c>
       <c r="F1456" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1456" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1456" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I1456" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1456" s="2" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="K1456" s="2" t="n">
-        <v>-172</v>
+        <v>-186</v>
       </c>
       <c r="L1456" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1456" s="2" t="inlineStr">
         <is>
@@ -83053,23 +83053,23 @@
       </c>
       <c r="F1457" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1457" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1457" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1457" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1457" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K1457" s="3" t="n">
-        <v>-181</v>
+        <v>-183</v>
       </c>
       <c r="L1457" s="3" t="n">
         <v>0</v>
@@ -83104,23 +83104,23 @@
       </c>
       <c r="F1458" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1458" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1458" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I1458" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1458" s="2" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K1458" s="2" t="n">
-        <v>-174</v>
+        <v>-181</v>
       </c>
       <c r="L1458" s="2" t="n">
         <v>0</v>
@@ -84022,26 +84022,26 @@
       </c>
       <c r="F1476" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1476" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1476" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I1476" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1476" s="2" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K1476" s="2" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="L1476" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1476" s="2" t="inlineStr">
         <is>
@@ -84073,26 +84073,26 @@
       </c>
       <c r="F1477" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1477" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1477" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I1477" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J1477" s="3" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K1477" s="3" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="L1477" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1477" s="3" t="inlineStr">
         <is>
@@ -84226,26 +84226,26 @@
       </c>
       <c r="F1480" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1480" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1480" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I1480" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1480" s="2" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K1480" s="2" t="n">
-        <v>-169</v>
+        <v>-175</v>
       </c>
       <c r="L1480" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1480" s="2" t="inlineStr">
         <is>
@@ -84277,26 +84277,26 @@
       </c>
       <c r="F1481" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1481" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1481" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I1481" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1481" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K1481" s="3" t="n">
-        <v>-175</v>
+        <v>-172</v>
       </c>
       <c r="L1481" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1481" s="3" t="inlineStr">
         <is>
@@ -84328,23 +84328,23 @@
       </c>
       <c r="F1482" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1482" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1482" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I1482" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J1482" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K1482" s="2" t="n">
-        <v>-172</v>
+        <v>-169</v>
       </c>
       <c r="L1482" s="2" t="n">
         <v>0</v>
@@ -84532,26 +84532,26 @@
       </c>
       <c r="F1486" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1486" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1486" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I1486" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1486" s="2" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="K1486" s="2" t="n">
-        <v>-205</v>
+        <v>-197</v>
       </c>
       <c r="L1486" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1486" s="2" t="inlineStr">
         <is>
@@ -84583,23 +84583,23 @@
       </c>
       <c r="F1487" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1487" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1487" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I1487" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J1487" s="3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K1487" s="3" t="n">
-        <v>-199</v>
+        <v>-197</v>
       </c>
       <c r="L1487" s="3" t="n">
         <v>0</v>
@@ -84634,26 +84634,26 @@
       </c>
       <c r="F1488" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1488" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1488" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I1488" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1488" s="2" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K1488" s="2" t="n">
-        <v>-197</v>
+        <v>-205</v>
       </c>
       <c r="L1488" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1488" s="2" t="inlineStr">
         <is>
@@ -84685,26 +84685,26 @@
       </c>
       <c r="F1489" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1489" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1489" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I1489" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1489" s="3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K1489" s="3" t="n">
-        <v>-206</v>
+        <v>-199</v>
       </c>
       <c r="L1489" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1489" s="3" t="inlineStr">
         <is>
@@ -84736,26 +84736,26 @@
       </c>
       <c r="F1490" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1490" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1490" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I1490" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1490" s="2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K1490" s="2" t="n">
-        <v>-197</v>
+        <v>-206</v>
       </c>
       <c r="L1490" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1490" s="2" t="inlineStr">
         <is>
@@ -85654,23 +85654,23 @@
       </c>
       <c r="F1508" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1508" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1508" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I1508" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J1508" s="2" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="K1508" s="2" t="n">
-        <v>-119</v>
+        <v>-113</v>
       </c>
       <c r="L1508" s="2" t="n">
         <v>0</v>
@@ -85705,23 +85705,23 @@
       </c>
       <c r="F1509" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1509" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1509" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I1509" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J1509" s="3" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K1509" s="3" t="n">
-        <v>-113</v>
+        <v>-119</v>
       </c>
       <c r="L1509" s="3" t="n">
         <v>0</v>
@@ -85858,23 +85858,23 @@
       </c>
       <c r="F1512" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1512" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1512" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I1512" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1512" s="2" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K1512" s="2" t="n">
-        <v>-187</v>
+        <v>-197</v>
       </c>
       <c r="L1512" s="2" t="n">
         <v>0</v>
@@ -85909,23 +85909,23 @@
       </c>
       <c r="F1513" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1513" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1513" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1513" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1513" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K1513" s="3" t="n">
-        <v>-197</v>
+        <v>-195</v>
       </c>
       <c r="L1513" s="3" t="n">
         <v>0</v>
@@ -85960,23 +85960,23 @@
       </c>
       <c r="F1514" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1514" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1514" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I1514" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J1514" s="2" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K1514" s="2" t="n">
-        <v>-195</v>
+        <v>-187</v>
       </c>
       <c r="L1514" s="2" t="n">
         <v>0</v>
@@ -86164,26 +86164,26 @@
       </c>
       <c r="F1518" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1518" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1518" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I1518" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1518" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K1518" s="2" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="L1518" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1518" s="2" t="inlineStr">
         <is>
@@ -86215,26 +86215,26 @@
       </c>
       <c r="F1519" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1519" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1519" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I1519" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1519" s="3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K1519" s="3" t="n">
-        <v>-219</v>
+        <v>-222</v>
       </c>
       <c r="L1519" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1519" s="3" t="inlineStr">
         <is>
@@ -86266,26 +86266,26 @@
       </c>
       <c r="F1520" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1520" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1520" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I1520" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1520" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K1520" s="2" t="n">
-        <v>-222</v>
+        <v>-220</v>
       </c>
       <c r="L1520" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1520" s="2" t="inlineStr">
         <is>
@@ -86317,23 +86317,23 @@
       </c>
       <c r="F1521" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1521" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1521" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I1521" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J1521" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K1521" s="3" t="n">
-        <v>-218</v>
+        <v>-219</v>
       </c>
       <c r="L1521" s="3" t="n">
         <v>0</v>
@@ -86368,26 +86368,26 @@
       </c>
       <c r="F1522" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1522" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1522" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I1522" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1522" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K1522" s="2" t="n">
-        <v>-222</v>
+        <v>-218</v>
       </c>
       <c r="L1522" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1522" s="2" t="inlineStr">
         <is>
@@ -87194,10 +87194,10 @@
         <v>20</v>
       </c>
       <c r="I1538" s="2" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J1538" s="2" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="K1538" s="2" t="n">
         <v>0</v>
@@ -87245,13 +87245,13 @@
         <v>25</v>
       </c>
       <c r="I1539" s="3" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J1539" s="3" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="K1539" s="3" t="n">
-        <v>-127</v>
+        <v>-132</v>
       </c>
       <c r="L1539" s="3" t="n">
         <v>0</v>
@@ -87286,23 +87286,23 @@
       </c>
       <c r="F1540" s="2" t="inlineStr">
         <is>
-          <t>Alvaro Carpe</t>
+          <t>Brian Uriarte</t>
         </is>
       </c>
       <c r="G1540" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1540" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I1540" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J1540" s="2" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="K1540" s="2" t="n">
-        <v>-135</v>
+        <v>-148</v>
       </c>
       <c r="L1540" s="2" t="n">
         <v>0</v>
@@ -87337,23 +87337,23 @@
       </c>
       <c r="F1541" s="3" t="inlineStr">
         <is>
-          <t>Brian Uriarte</t>
+          <t>Alvaro Carpe</t>
         </is>
       </c>
       <c r="G1541" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1541" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1541" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J1541" s="3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K1541" s="3" t="n">
-        <v>-139</v>
+        <v>-160</v>
       </c>
       <c r="L1541" s="3" t="n">
         <v>0</v>
@@ -87404,7 +87404,7 @@
         <v>146</v>
       </c>
       <c r="K1542" s="2" t="n">
-        <v>-180</v>
+        <v>-205</v>
       </c>
       <c r="L1542" s="2" t="n">
         <v>0</v>
@@ -87449,13 +87449,13 @@
         <v>2</v>
       </c>
       <c r="I1543" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J1543" s="3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K1543" s="3" t="n">
-        <v>-206</v>
+        <v>-228</v>
       </c>
       <c r="L1543" s="3" t="n">
         <v>0</v>
@@ -87490,23 +87490,23 @@
       </c>
       <c r="F1544" s="2" t="inlineStr">
         <is>
-          <t>Hakim Danish</t>
+          <t>Veda Pratama</t>
         </is>
       </c>
       <c r="G1544" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1544" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1544" s="2" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J1544" s="2" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K1544" s="2" t="n">
-        <v>-221</v>
+        <v>-236</v>
       </c>
       <c r="L1544" s="2" t="n">
         <v>0</v>
@@ -87541,23 +87541,23 @@
       </c>
       <c r="F1545" s="3" t="inlineStr">
         <is>
-          <t>Veda Pratama</t>
+          <t>Matteo Bertelle</t>
         </is>
       </c>
       <c r="G1545" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1545" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I1545" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J1545" s="3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K1545" s="3" t="n">
-        <v>-221</v>
+        <v>-242</v>
       </c>
       <c r="L1545" s="3" t="n">
         <v>0</v>
@@ -87592,23 +87592,23 @@
       </c>
       <c r="F1546" s="2" t="inlineStr">
         <is>
-          <t>Matteo Bertelle</t>
+          <t>Hakim Danish</t>
         </is>
       </c>
       <c r="G1546" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1546" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I1546" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1546" s="2" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="K1546" s="2" t="n">
-        <v>-230</v>
+        <v>-244</v>
       </c>
       <c r="L1546" s="2" t="n">
         <v>0</v>
@@ -87653,13 +87653,13 @@
         <v>11</v>
       </c>
       <c r="I1547" s="3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J1547" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K1547" s="3" t="n">
-        <v>-245</v>
+        <v>-259</v>
       </c>
       <c r="L1547" s="3" t="n">
         <v>0</v>
@@ -87704,13 +87704,13 @@
         <v>6</v>
       </c>
       <c r="I1548" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J1548" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K1548" s="2" t="n">
-        <v>-247</v>
+        <v>-268</v>
       </c>
       <c r="L1548" s="2" t="n">
         <v>0</v>
@@ -87755,13 +87755,13 @@
         <v>0</v>
       </c>
       <c r="I1549" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J1549" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K1549" s="3" t="n">
-        <v>-256</v>
+        <v>-273</v>
       </c>
       <c r="L1549" s="3" t="n">
         <v>0</v>
@@ -87796,23 +87796,23 @@
       </c>
       <c r="F1550" s="2" t="inlineStr">
         <is>
-          <t>Casey O'gorman</t>
+          <t>Joel Esteban</t>
         </is>
       </c>
       <c r="G1550" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1550" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I1550" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J1550" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K1550" s="2" t="n">
-        <v>-256</v>
+        <v>-278</v>
       </c>
       <c r="L1550" s="2" t="n">
         <v>0</v>
@@ -87847,23 +87847,23 @@
       </c>
       <c r="F1551" s="3" t="inlineStr">
         <is>
-          <t>Joel Kelso</t>
+          <t>Adrian Fernandez</t>
         </is>
       </c>
       <c r="G1551" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H1551" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1551" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J1551" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K1551" s="3" t="n">
-        <v>-259</v>
+        <v>-280</v>
       </c>
       <c r="L1551" s="3" t="n">
         <v>0</v>
@@ -87898,23 +87898,23 @@
       </c>
       <c r="F1552" s="2" t="inlineStr">
         <is>
-          <t>Joel Esteban</t>
+          <t>Casey O'gorman</t>
         </is>
       </c>
       <c r="G1552" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1552" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I1552" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J1552" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K1552" s="2" t="n">
-        <v>-260</v>
+        <v>-281</v>
       </c>
       <c r="L1552" s="2" t="n">
         <v>0</v>
@@ -87949,7 +87949,7 @@
       </c>
       <c r="F1553" s="3" t="inlineStr">
         <is>
-          <t>Eddie O'shea</t>
+          <t>Joel Kelso</t>
         </is>
       </c>
       <c r="G1553" s="3" t="n">
@@ -87959,13 +87959,13 @@
         <v>0</v>
       </c>
       <c r="I1553" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1553" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K1553" s="3" t="n">
-        <v>-261</v>
+        <v>-284</v>
       </c>
       <c r="L1553" s="3" t="n">
         <v>0</v>
@@ -88000,23 +88000,23 @@
       </c>
       <c r="F1554" s="2" t="inlineStr">
         <is>
-          <t>Adrian Fernandez</t>
+          <t>Eddie O'shea</t>
         </is>
       </c>
       <c r="G1554" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H1554" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1554" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1554" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K1554" s="2" t="n">
-        <v>-264</v>
+        <v>-286</v>
       </c>
       <c r="L1554" s="2" t="n">
         <v>0</v>
@@ -88067,7 +88067,7 @@
         <v>61</v>
       </c>
       <c r="K1555" s="3" t="n">
-        <v>-265</v>
+        <v>-290</v>
       </c>
       <c r="L1555" s="3" t="n">
         <v>0</v>
@@ -88112,16 +88112,16 @@
         <v>0</v>
       </c>
       <c r="I1556" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1556" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1556" s="2" t="n">
-        <v>-277</v>
+        <v>-301</v>
       </c>
       <c r="L1556" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1556" s="2" t="inlineStr">
         <is>
@@ -88163,13 +88163,13 @@
         <v>8</v>
       </c>
       <c r="I1557" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J1557" s="3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K1557" s="3" t="n">
-        <v>-287</v>
+        <v>-307</v>
       </c>
       <c r="L1557" s="3" t="n">
         <v>0</v>
@@ -88214,16 +88214,16 @@
         <v>0</v>
       </c>
       <c r="I1558" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1558" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K1558" s="2" t="n">
-        <v>-296</v>
+        <v>-315</v>
       </c>
       <c r="L1558" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1558" s="2" t="inlineStr">
         <is>
@@ -88271,7 +88271,7 @@
         <v>7</v>
       </c>
       <c r="K1559" s="3" t="n">
-        <v>-319</v>
+        <v>-344</v>
       </c>
       <c r="L1559" s="3" t="n">
         <v>1</v>
@@ -88322,7 +88322,7 @@
         <v>6</v>
       </c>
       <c r="K1560" s="2" t="n">
-        <v>-320</v>
+        <v>-345</v>
       </c>
       <c r="L1560" s="2" t="n">
         <v>1</v>
@@ -88373,7 +88373,7 @@
         <v>5</v>
       </c>
       <c r="K1561" s="3" t="n">
-        <v>-321</v>
+        <v>-346</v>
       </c>
       <c r="L1561" s="3" t="n">
         <v>1</v>
@@ -88424,7 +88424,7 @@
         <v>4</v>
       </c>
       <c r="K1562" s="2" t="n">
-        <v>-322</v>
+        <v>-347</v>
       </c>
       <c r="L1562" s="2" t="n">
         <v>1</v>
@@ -88475,7 +88475,7 @@
         <v>2</v>
       </c>
       <c r="K1563" s="3" t="n">
-        <v>-324</v>
+        <v>-349</v>
       </c>
       <c r="L1563" s="3" t="n">
         <v>0</v>
@@ -88526,7 +88526,7 @@
         <v>1</v>
       </c>
       <c r="K1564" s="2" t="n">
-        <v>-325</v>
+        <v>-350</v>
       </c>
       <c r="L1564" s="2" t="n">
         <v>1</v>
@@ -88577,7 +88577,7 @@
         <v>1</v>
       </c>
       <c r="K1565" s="3" t="n">
-        <v>-325</v>
+        <v>-350</v>
       </c>
       <c r="L1565" s="3" t="n">
         <v>1</v>
@@ -88628,7 +88628,7 @@
         <v>0</v>
       </c>
       <c r="K1566" s="2" t="n">
-        <v>-326</v>
+        <v>-351</v>
       </c>
       <c r="L1566" s="2" t="n">
         <v>1</v>
@@ -88679,7 +88679,7 @@
         <v>0</v>
       </c>
       <c r="K1567" s="3" t="n">
-        <v>-326</v>
+        <v>-351</v>
       </c>
       <c r="L1567" s="3" t="n">
         <v>1</v>
@@ -88730,7 +88730,7 @@
         <v>0</v>
       </c>
       <c r="K1568" s="2" t="n">
-        <v>-326</v>
+        <v>-351</v>
       </c>
       <c r="L1568" s="2" t="n">
         <v>1</v>
@@ -88781,7 +88781,7 @@
         <v>0</v>
       </c>
       <c r="K1569" s="3" t="n">
-        <v>-326</v>
+        <v>-351</v>
       </c>
       <c r="L1569" s="3" t="n">
         <v>1</v>

--- a/exports/motorsport_database_2026.xlsx
+++ b/exports/motorsport_database_2026.xlsx
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr"/>
@@ -4181,14 +4181,14 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Charles Leclerc</t>
+          <t>Max Verstappen</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
@@ -4207,14 +4207,14 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Max Verstappen</t>
+          <t>Charles Leclerc</t>
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr"/>
@@ -4344,7 +4344,7 @@
         <v>41</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
@@ -4370,7 +4370,7 @@
         <v>38</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
         <v>27</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
@@ -4422,7 +4422,7 @@
         <v>23</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
@@ -4441,14 +4441,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Bortoleto</t>
+          <t>Nico Hülkenberg</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Nico Hülkenberg</t>
+          <t>Gabriel Bortoleto</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
         <v>7</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
         <v>7</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
@@ -4578,7 +4578,7 @@
         <v>5</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>

--- a/exports/motorsport_database_2026.xlsx
+++ b/exports/motorsport_database_2026.xlsx
@@ -513,20 +513,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3">
@@ -543,20 +543,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>222</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>67</v>
@@ -603,20 +603,20 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -633,20 +633,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>68</v>
@@ -700,7 +700,7 @@
         <v>236</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>66</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>62</v>
@@ -760,7 +760,7 @@
         <v>166</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>62</v>
@@ -790,7 +790,7 @@
         <v>125</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>22</v>
@@ -820,7 +820,7 @@
         <v>122</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>20</v>
@@ -850,7 +850,7 @@
         <v>108</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>7</v>
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>12</v>
@@ -903,20 +903,20 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -933,20 +933,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
         <v>74</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -970,7 +970,7 @@
         <v>59</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>12</v>
@@ -1000,7 +1000,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15</v>
@@ -1030,7 +1030,7 @@
         <v>33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>10</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         <v>18</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -8848,23 +8848,23 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-14</v>
+        <v>-23</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -8899,23 +8899,23 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>0</v>
@@ -9001,23 +9001,23 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>0</v>
@@ -9052,23 +9052,23 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -9511,23 +9511,23 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
@@ -9562,23 +9562,23 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -10480,23 +10480,23 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-11</v>
+        <v>-22</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -10531,23 +10531,23 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0</v>
@@ -10633,23 +10633,23 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
@@ -10684,23 +10684,23 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-14</v>
+        <v>-23</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -11143,17 +11143,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>6</v>
@@ -11194,17 +11194,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>6</v>
@@ -12112,23 +12112,23 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-4</v>
+        <v>-36</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -12163,23 +12163,23 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>-36</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -12265,23 +12265,23 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>-44</v>
+        <v>-21</v>
       </c>
       <c r="L69" s="3" t="n">
         <v>0</v>
@@ -12316,23 +12316,23 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-21</v>
+        <v>-44</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -12775,26 +12775,26 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>-75</v>
+        <v>-72</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -12826,26 +12826,26 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>-72</v>
+        <v>-75</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -13744,23 +13744,23 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>-11</v>
+        <v>-44</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -13795,23 +13795,23 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-44</v>
+        <v>-11</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>0</v>
@@ -13897,23 +13897,23 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>-53</v>
+        <v>-35</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>0</v>
@@ -13948,23 +13948,23 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>-35</v>
+        <v>-53</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -14407,26 +14407,26 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>-90</v>
+        <v>-92</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -14458,26 +14458,26 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>-92</v>
+        <v>-90</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
@@ -15376,26 +15376,26 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>-1</v>
+        <v>-71</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -15427,26 +15427,26 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>-71</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -15529,23 +15529,23 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>-61</v>
+        <v>-45</v>
       </c>
       <c r="L133" s="3" t="n">
         <v>0</v>
@@ -15580,23 +15580,23 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>-45</v>
+        <v>-61</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -16039,23 +16039,23 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I143" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J143" s="3" t="n">
-        <v>26</v>
-      </c>
       <c r="K143" s="3" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="L143" s="3" t="n">
         <v>0</v>
@@ -16090,23 +16090,23 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -17021,10 +17021,10 @@
         <v>0</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>-15</v>
+        <v>-85</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>1</v>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -17072,10 +17072,10 @@
         <v>0</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="K163" s="3" t="n">
-        <v>-85</v>
+        <v>-15</v>
       </c>
       <c r="L163" s="3" t="n">
         <v>1</v>
@@ -17161,23 +17161,23 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K165" s="3" t="n">
-        <v>-65</v>
+        <v>-50</v>
       </c>
       <c r="L165" s="3" t="n">
         <v>0</v>
@@ -17212,23 +17212,23 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>-50</v>
+        <v>-65</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -17671,23 +17671,23 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>-105</v>
+        <v>-125</v>
       </c>
       <c r="L175" s="3" t="n">
         <v>0</v>
@@ -17722,23 +17722,23 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>-125</v>
+        <v>-105</v>
       </c>
       <c r="L176" s="2" t="n">
         <v>0</v>
@@ -18640,23 +18640,23 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H194" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H194" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="I194" s="2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>-17</v>
+        <v>-102</v>
       </c>
       <c r="L194" s="2" t="n">
         <v>0</v>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G195" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="K195" s="3" t="n">
-        <v>-102</v>
+        <v>-17</v>
       </c>
       <c r="L195" s="3" t="n">
         <v>0</v>
@@ -18793,23 +18793,23 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G197" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K197" s="3" t="n">
-        <v>-81</v>
+        <v>-70</v>
       </c>
       <c r="L197" s="3" t="n">
         <v>0</v>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>-70</v>
+        <v>-81</v>
       </c>
       <c r="L198" s="2" t="n">
         <v>0</v>
@@ -19303,26 +19303,26 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G207" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J207" s="3" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K207" s="3" t="n">
-        <v>-136</v>
+        <v>-150</v>
       </c>
       <c r="L207" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -19354,26 +19354,26 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>-150</v>
+        <v>-136</v>
       </c>
       <c r="L208" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
@@ -20272,23 +20272,23 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="K226" s="2" t="n">
-        <v>-20</v>
+        <v>-72</v>
       </c>
       <c r="L226" s="2" t="n">
         <v>0</v>
@@ -20323,23 +20323,23 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G227" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J227" s="3" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="K227" s="3" t="n">
-        <v>-72</v>
+        <v>-20</v>
       </c>
       <c r="L227" s="3" t="n">
         <v>0</v>
@@ -20425,23 +20425,23 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G229" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J229" s="3" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="K229" s="3" t="n">
-        <v>-75</v>
+        <v>-48</v>
       </c>
       <c r="L229" s="3" t="n">
         <v>0</v>
@@ -20476,23 +20476,23 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>-48</v>
+        <v>-75</v>
       </c>
       <c r="L230" s="2" t="n">
         <v>0</v>
@@ -20935,26 +20935,26 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G239" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H239" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J239" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K239" s="3" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="L239" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -20986,26 +20986,26 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K240" s="2" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="L240" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
@@ -21904,23 +21904,23 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>-8</v>
+        <v>-40</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>0</v>
@@ -21955,23 +21955,23 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G259" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H259" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H259" s="3" t="n">
-        <v>25</v>
-      </c>
       <c r="I259" s="3" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J259" s="3" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="K259" s="3" t="n">
-        <v>-40</v>
+        <v>-8</v>
       </c>
       <c r="L259" s="3" t="n">
         <v>0</v>
@@ -22057,26 +22057,26 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G261" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J261" s="3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>-46</v>
+        <v>-48</v>
       </c>
       <c r="L261" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
@@ -22108,26 +22108,26 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>-48</v>
+        <v>-46</v>
       </c>
       <c r="L262" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
@@ -22567,26 +22567,26 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G271" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I271" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J271" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K271" s="3" t="n">
-        <v>-143</v>
+        <v>-139</v>
       </c>
       <c r="L271" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -22618,26 +22618,26 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G272" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H272" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>-139</v>
+        <v>-143</v>
       </c>
       <c r="L272" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
@@ -23536,23 +23536,23 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L290" s="2" t="n">
         <v>0</v>
@@ -23587,23 +23587,23 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G291" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I291" s="3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J291" s="3" t="n">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="K291" s="3" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L291" s="3" t="n">
         <v>0</v>
@@ -23689,23 +23689,23 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G293" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I293" s="3" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J293" s="3" t="n">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="K293" s="3" t="n">
-        <v>-25</v>
+        <v>-60</v>
       </c>
       <c r="L293" s="3" t="n">
         <v>0</v>
@@ -23740,23 +23740,23 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="L294" s="2" t="n">
         <v>0</v>
@@ -24199,23 +24199,23 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G303" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H303" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I303" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J303" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K303" s="3" t="n">
-        <v>-148</v>
+        <v>-150</v>
       </c>
       <c r="L303" s="3" t="n">
         <v>0</v>
@@ -24250,23 +24250,23 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G304" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K304" s="2" t="n">
-        <v>-150</v>
+        <v>-148</v>
       </c>
       <c r="L304" s="2" t="n">
         <v>0</v>
@@ -25168,23 +25168,23 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G322" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L322" s="2" t="n">
         <v>0</v>
@@ -25219,23 +25219,23 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G323" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H323" s="3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I323" s="3" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J323" s="3" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="K323" s="3" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="L323" s="3" t="n">
         <v>0</v>
@@ -25321,23 +25321,23 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G325" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H325" s="3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I325" s="3" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J325" s="3" t="n">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="K325" s="3" t="n">
-        <v>-14</v>
+        <v>-60</v>
       </c>
       <c r="L325" s="3" t="n">
         <v>0</v>
@@ -25372,23 +25372,23 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G326" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>-60</v>
+        <v>-14</v>
       </c>
       <c r="L326" s="2" t="n">
         <v>0</v>
@@ -25831,23 +25831,23 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I335" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J335" s="3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K335" s="3" t="n">
-        <v>-153</v>
+        <v>-160</v>
       </c>
       <c r="L335" s="3" t="n">
         <v>0</v>
@@ -25882,23 +25882,23 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G336" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J336" s="2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>-160</v>
+        <v>-153</v>
       </c>
       <c r="L336" s="2" t="n">
         <v>0</v>
@@ -26800,23 +26800,23 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G354" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="K354" s="2" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L354" s="2" t="n">
         <v>0</v>
@@ -26851,23 +26851,23 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G355" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H355" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I355" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J355" s="3" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K355" s="3" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L355" s="3" t="n">
         <v>0</v>
@@ -26953,23 +26953,23 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G357" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H357" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I357" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J357" s="3" t="n">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="K357" s="3" t="n">
-        <v>-37</v>
+        <v>-77</v>
       </c>
       <c r="L357" s="3" t="n">
         <v>0</v>
@@ -27004,23 +27004,23 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G358" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H358" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="K358" s="2" t="n">
-        <v>-77</v>
+        <v>-37</v>
       </c>
       <c r="L358" s="2" t="n">
         <v>0</v>
@@ -27463,26 +27463,26 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G367" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I367" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J367" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K367" s="3" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="L367" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
@@ -27514,26 +27514,26 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G368" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K368" s="2" t="n">
-        <v>-186</v>
+        <v>-185</v>
       </c>
       <c r="L368" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M368" s="2" t="inlineStr">
         <is>
@@ -28432,23 +28432,23 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J386" s="2" t="n">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="K386" s="2" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L386" s="2" t="n">
         <v>0</v>
@@ -28483,23 +28483,23 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G387" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H387" s="3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I387" s="3" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="J387" s="3" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K387" s="3" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="L387" s="3" t="n">
         <v>0</v>
@@ -28585,26 +28585,26 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G389" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I389" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J389" s="3" t="n">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K389" s="3" t="n">
-        <v>-53</v>
+        <v>-67</v>
       </c>
       <c r="L389" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -28636,26 +28636,26 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G390" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H390" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="K390" s="2" t="n">
-        <v>-67</v>
+        <v>-53</v>
       </c>
       <c r="L390" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M390" s="2" t="inlineStr">
         <is>
@@ -29095,26 +29095,26 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G399" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H399" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I399" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J399" s="3" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K399" s="3" t="n">
-        <v>-201</v>
+        <v>-192</v>
       </c>
       <c r="L399" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -29146,26 +29146,26 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G400" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H400" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K400" s="2" t="n">
-        <v>-192</v>
+        <v>-201</v>
       </c>
       <c r="L400" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M400" s="2" t="inlineStr">
         <is>
@@ -30064,17 +30064,17 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G418" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H418" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J418" s="2" t="n">
         <v>274</v>
@@ -30115,17 +30115,17 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G419" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I419" s="3" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J419" s="3" t="n">
         <v>274</v>
@@ -30217,26 +30217,26 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G421" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H421" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I421" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J421" s="3" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K421" s="3" t="n">
-        <v>-71</v>
+        <v>-65</v>
       </c>
       <c r="L421" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -30268,26 +30268,26 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G422" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H422" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J422" s="2" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>-65</v>
+        <v>-71</v>
       </c>
       <c r="L422" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" s="2" t="inlineStr">
         <is>
@@ -30727,26 +30727,26 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G431" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I431" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J431" s="3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K431" s="3" t="n">
-        <v>-213</v>
+        <v>-210</v>
       </c>
       <c r="L431" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -30778,26 +30778,26 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G432" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I432" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J432" s="2" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>-210</v>
+        <v>-213</v>
       </c>
       <c r="L432" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M432" s="2" t="inlineStr">
         <is>
@@ -31696,23 +31696,23 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G450" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H450" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I450" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I450" s="2" t="n">
-        <v>32</v>
-      </c>
       <c r="J450" s="2" t="n">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="K450" s="2" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L450" s="2" t="n">
         <v>0</v>
@@ -31747,23 +31747,23 @@
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G451" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H451" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I451" s="3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J451" s="3" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="K451" s="3" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L451" s="3" t="n">
         <v>0</v>
@@ -31849,23 +31849,23 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G453" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I453" s="3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J453" s="3" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="K453" s="3" t="n">
-        <v>-84</v>
+        <v>-72</v>
       </c>
       <c r="L453" s="3" t="n">
         <v>0</v>
@@ -31900,23 +31900,23 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G454" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H454" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>-72</v>
+        <v>-84</v>
       </c>
       <c r="L454" s="2" t="n">
         <v>0</v>
@@ -32359,26 +32359,26 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G463" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I463" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J463" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K463" s="3" t="n">
-        <v>-245</v>
+        <v>-241</v>
       </c>
       <c r="L463" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
@@ -32410,26 +32410,26 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G464" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H464" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J464" s="2" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K464" s="2" t="n">
-        <v>-241</v>
+        <v>-245</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M464" s="2" t="inlineStr">
         <is>
@@ -33328,23 +33328,23 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G482" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H482" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I482" s="2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J482" s="2" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K482" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L482" s="2" t="n">
         <v>0</v>
@@ -33379,23 +33379,23 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G483" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I483" s="3" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J483" s="3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K483" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L483" s="3" t="n">
         <v>0</v>
@@ -33481,23 +33481,23 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G485" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I485" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J485" s="3" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K485" s="3" t="n">
-        <v>-96</v>
+        <v>-90</v>
       </c>
       <c r="L485" s="3" t="n">
         <v>0</v>
@@ -33532,23 +33532,23 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G486" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H486" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="K486" s="2" t="n">
-        <v>-90</v>
+        <v>-96</v>
       </c>
       <c r="L486" s="2" t="n">
         <v>0</v>
@@ -33991,23 +33991,23 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G495" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J495" s="3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K495" s="3" t="n">
-        <v>-267</v>
+        <v>-259</v>
       </c>
       <c r="L495" s="3" t="n">
         <v>0</v>
@@ -34042,23 +34042,23 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G496" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H496" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I496" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J496" s="2" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K496" s="2" t="n">
-        <v>-259</v>
+        <v>-267</v>
       </c>
       <c r="L496" s="2" t="n">
         <v>0</v>
@@ -34960,23 +34960,23 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>Jorge Martin</t>
+          <t>Marc Marquez</t>
         </is>
       </c>
       <c r="G514" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H514" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I514" s="2" t="n">
         <v>22</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K514" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L514" s="2" t="n">
         <v>0</v>
@@ -35011,23 +35011,23 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>Marc Marquez</t>
+          <t>Jorge Martin</t>
         </is>
       </c>
       <c r="G515" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I515" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J515" s="3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K515" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L515" s="3" t="n">
         <v>0</v>
@@ -35113,23 +35113,23 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>Ai Ogura</t>
+          <t>Pedro Acosta</t>
         </is>
       </c>
       <c r="G517" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I517" s="3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J517" s="3" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K517" s="3" t="n">
-        <v>-96</v>
+        <v>-97</v>
       </c>
       <c r="L517" s="3" t="n">
         <v>0</v>
@@ -35164,23 +35164,23 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>Pedro Acosta</t>
+          <t>Ai Ogura</t>
         </is>
       </c>
       <c r="G518" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H518" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I518" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J518" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K518" s="2" t="n">
-        <v>-97</v>
+        <v>-96</v>
       </c>
       <c r="L518" s="2" t="n">
         <v>0</v>
@@ -35623,17 +35623,17 @@
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
-          <t>Fabio Quartararo</t>
+          <t>Diogo Moreira</t>
         </is>
       </c>
       <c r="G527" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H527" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I527" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J527" s="3" t="n">
         <v>74</v>
@@ -35642,7 +35642,7 @@
         <v>-281</v>
       </c>
       <c r="L527" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M527" s="3" t="inlineStr">
         <is>
@@ -35674,17 +35674,17 @@
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>Diogo Moreira</t>
+          <t>Fabio Quartararo</t>
         </is>
       </c>
       <c r="G528" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H528" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J528" s="2" t="n">
         <v>74</v>
@@ -35693,7 +35693,7 @@
         <v>-281</v>
       </c>
       <c r="L528" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M528" s="2" t="inlineStr">
         <is>

--- a/exports/motorsport_database_2026.xlsx
+++ b/exports/motorsport_database_2026.xlsx
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>75</v>
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>12</v>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>16</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
